--- a/translation/un.xlsx
+++ b/translation/un.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="un" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A890"/>
+  <dimension ref="A1:A730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,84 +428,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>「ぷっ」って笑ったね・・・
 　　　確かに・・酷いヤツ・・・
 　　　祐二って・・・</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>祐里子！！</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>とっさに柚を頼ろうとしたけど
 柚はＰＨＳで一人チャルメラを
@@ -513,107 +457,23 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「あ・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「よっ、じゃないわよ！
-　　この変態！！！
-　　また私を押し倒すつもり！！！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「なにが解けたよ・・・
-　　人のパンツあんなに
-　　嘗める様に見ておいて！！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>祐二君♪</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「昨日、校門で
-　　私の事いきなり押し倒して〜」</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「その挙げ句、私のパンツ
-　　ジロジロと嘗める様にして
-　　見つめてました！！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「なによ・・その手帳って・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>ちゃんと名前だって
 　　「御幸 春菜」って書いてあったし</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「・・・春菜・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>春菜（菜摘）「残念でした、それは私の妹よ！！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>そうよ！
 　　　私は「御幸 菜摘」（みゆき なつみ）
@@ -621,267 +481,85 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>！！！！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>祐二君！</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>祐里子？</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>！？</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>祐二？</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>柚！！！</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>！</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">        ｂｙ  ぷりてぃーさんた」</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>な・・なんだこりゃ・・・</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>この独特の文字・・・</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>それは誰が
 誰に宛てた物なのか・・・
@@ -889,8 +567,8 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>久遠のやつ・・・
 　　でも・・・俺が
@@ -898,8 +576,8 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>久遠は自分が言う様に
 本当に未来が
@@ -907,15 +585,15 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>・・・・・くすっ</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>でも・・それも
 そんなに不思議な事じゃないかな・・・
@@ -923,8 +601,8 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>久遠がいなければ
 俺はこんな風に立ち直る事も
@@ -932,16 +610,16 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>身近にいた
 とても大切な存在として</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>久遠に特別な想いが
 芽生えているのは
@@ -949,8 +627,8 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>その久遠の為にも
 そして・・・現れる事の無い
@@ -958,8 +636,8 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>俺はもう少し
 柚の為だけにここで
@@ -967,15 +645,15 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>メリークリスマス・・・</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>クスッ・・・
 　　そのカード・・・
@@ -983,38 +661,38 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>え・・・ええ・・・</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>そう・・・ここで
 　　誰を待っているの？</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>・・・・・いや・・・</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>いきなり見知らぬ
 女性に声をかけられた俺・・・</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>でも、なにも答える事が
 出来ずにそのまま
@@ -1022,8 +700,8 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>まさか・・・既にいない
 彼女を待っているなどと
@@ -1031,55 +709,55 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>するとその女性は
 聞くのをあきらめたのか</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>振り返って
 俺の前から立ち去ろうとする</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>そして・・・
 その刹那・・・</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>・・・運命は
 　　・・・一つじゃないわ</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>でも・・・終焉は
 　　たった一つ・・・ね</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>・・・えっ・・・？</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>それだけを言うと
 今度は振り返る事無く
@@ -1087,32 +765,32 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>・・・今の・・・
 　　どういう・・・意味だ？</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>一体、今の女性が誰なのか
 俺には見当も付かなかった</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>その意味深な言葉に
 しばらく気を取られつつも</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>俺はまたベンチの上に
 じっと座り込み
@@ -1120,8 +798,8 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>誰も来ない約束を終え
 俺はそろそろ日付も
@@ -1129,46 +807,46 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>自分の家へと着いた・・・</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>玄関に入ると久遠の靴が
 きちんと揃えて置いてある</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>久遠？</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>俺は久遠を呼びながら
 リビングへと向かった</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>リビングにも
 久遠はいない・・・</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>久遠のヤツ・・・
 きっとどこかに隠れてて
@@ -1176,24 +854,24 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>俺はリビングを出ると
 ２階の自分の部屋に向かった</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>おい・・・
 　　久遠・・出てこいよ</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>薄暗い部屋の
 明かりを点けようと手探りで
@@ -1201,63 +879,63 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>すると突然大きな声と共に
 部屋の明かりが点いた</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>じゃ〜〜ん
 　　サンタさんだぞ♪</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>・・・・・・・久遠</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>突然、サンタの格好（？）で
 久遠が目の前に現れる・・・</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>これが「ぷりてぃーさんた」の
 正体なんだろうか？？</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>・・・どこがサンタだ・・・
 　　サンタは普通おっさんだぞ・・・</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>お前のはコンパニオンって
 　　言うんじゃないのか？</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>ほら・・・よく
 　　クリスマスセールの時に
@@ -1265,8 +943,8 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>久遠って
 　　誰の事かな？？
@@ -1274,16 +952,16 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 挑発のつもりなのか</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>ミニスカートを
 ヒラヒラとさせながら
@@ -1291,16 +969,16 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>んじゃ
 　　サンタ、プレゼントくれ・・・</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>むぅ・・もう
 　　お兄ちゃんって
@@ -1308,56 +986,56 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>ボクずっと待ってたのに
 　　・・・こんな時間まで</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>久遠は
 少しすねた顔をすると</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>すぐなにかを思いついたかの様に
 ニコッと笑って俺に言う</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>あ・・・そういえば
 　　ボクのプレゼントは？？</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>今日はクリスマスだし・・・
 　　それにボクの誕生日だぞ</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>・・・サンタは
 　　プレゼントいらんだろ・・・</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>・・・・・・お兄ちゃん
 　　忘れてたんでしょ・・・
@@ -1365,16 +1043,16 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>久遠はぷぅと頬を膨らませて
 俺に抗議する・・・</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>俺もなんか物が物だけに
 ちょっと出すキッカケを
@@ -1382,39 +1060,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>ま・・・まぁ・・・
 　　今度、買いに行くから・・・</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>ぷぅ・・・</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 別に怒った風でも無く</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>やれやれといった顔を
 しながら俺に言った</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>・・・まぁ・・別にいいもん
 　　物なんていつだって
@@ -1422,8 +1100,8 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>それより、今日は
 　　クリスマスなんだから
@@ -1431,15 +1109,15 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>思い出？？</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>へへっ・・・二人だけの
 　　クリスマスパーティー・・・
@@ -1447,8 +1125,8 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>そう言って久遠は
 ナプキンを被せてある
@@ -1456,8 +1134,8 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>それじゃ・・・
 　　明かり消して
@@ -1465,8 +1143,8 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>そうそう
 　　そろそろ雪降るから
@@ -1474,8 +1152,8 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>はぁ・・・
 　　雪なんて降ってなかったぞ・・・
@@ -1483,95 +1161,95 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>さっきまで外にいたのだから
 それくらいは流石に分かる</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>でも、久遠は自信満々の顔で
 俺に言った・・</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>・・・ボクの予感は
 　　外れないよ・・絶対</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>俺は久遠の言う通り
 カーテンを開けて外を見る</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>すると窓の外ではいつの間にか
 深々と雪が降り始めていた</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>呆気にとられる俺・・・</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>思わず、今までの久遠との
 やり取りが頭にリフレインする</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>少し呆然とした俺を
 気にする事も無く</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>久遠はテーブルに座って
 キャンドルに明かりを灯した</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・
 　　そっち座って・・・</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>テーブルの上には
 久遠が作ったのか</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>小さなケーキと
 きれいに彩られた
@@ -1579,16 +1257,16 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>・・・これ・・・
 　　久遠が全部作ったのか？</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr">
         <is>
           <t>・・・へへっ♪
 　　全部、お兄ちゃんが
@@ -1596,16 +1274,16 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>このシャンパンも
 　　探すの大変だったんだから</t>
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="108">
+      <c r="A108" t="inlineStr">
         <is>
           <t>キャンドルの明かりに
 照らされてる久遠は
@@ -1613,32 +1291,32 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="109">
+      <c r="A109" t="inlineStr">
         <is>
           <t>年上の女性の様な雰囲気を
 醸し出している・・・</t>
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>俺はなんだか
 気恥ずかしくなってきて</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>まともに久遠の顔を見つめる事が
 出来なかった</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>・・・好きなって・・・
 　　確かに好きな食い物は揃ってるけど
@@ -1646,15 +1324,15 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>えっ・・あ・・・</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>ま、まぁ・・・
 　　これから好きになると思うよ
@@ -1662,39 +1340,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>少し言葉を濁しながら
 俺にシャンパンを注ぐ久遠</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>そして、二つのグラスに
 それが満たされると</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>久遠は片方のグラスを持って
 俺のグラスに近付けてきた</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>それじゃ・・・乾杯・・・</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>グラスを傾ける久遠は
 今まで俺の知っていた
@@ -1702,38 +1380,31 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>俺は緊張感が漂う雰囲気の中で
 シャンパンを飲み干した</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>よいしょっと・・・・</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>久遠はテーブルの上を
 綺麗に片付けると</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>俺のベッドの上に
 ちょこんと座って
@@ -1741,8 +1412,8 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>久遠・・・
 　　お前色んな料理
@@ -1750,8 +1421,8 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>へへっ♪練習したんだよ
 　　お兄ちゃんご飯になると
@@ -1759,8 +1430,8 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>飯といえば・・・
 この前久遠が作ってくれた時は
@@ -1768,8 +1439,8 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>もしかして・・・うるさいって
 あの時の事を
@@ -1777,8 +1448,8 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>ま・・まぁ・・・
 今考えると、あの時の俺は
@@ -1786,16 +1457,16 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>他の人を
 傷付けてばっかりだった</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>でも今、俺がこうやって
 恥ずかしく思えるのも
@@ -1803,16 +1474,16 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>色々と・・・
 　　ありがとな・・・久遠</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>本当に色々あり過ぎて
 久遠になにから感謝すればいいのか
@@ -1820,8 +1491,8 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>俺はそう言うのが
 今出来る精一杯の
@@ -1829,40 +1500,40 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>別に・・・
 　　ボクが好きでやってる事だし</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>久遠はなんでも
 無かったかの様に言うけど</t>
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>久遠にとっても、俺の態度は
 かなり堪え難かったハズだ・・・</t>
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+    <row r="137">
+      <c r="A137" t="inlineStr">
         <is>
           <t>それでも、久遠はいつも笑顔で
 接してくれていた・・・</t>
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>いつもガキだなんだと
 言ってはいたけど
@@ -1870,79 +1541,79 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t>それじゃ・・・そろそろ
 　　家送るか・・・</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>お向かいだけど
 　　こんな遅くじゃ怒られるだろ</t>
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>そう言って
 久遠に手を伸ばすと</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>久遠はその手を
 両手で握り返してくる</t>
         </is>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>へへっ・・・今日は
 　　ここに泊まるって言ってある</t>
         </is>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>・・・・・・・え？</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>だから・・・ボク
 　　今日はここ泊まってく・・・</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>まだ、ボクの
 　　プレゼントあげてないし</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>ちょっと待った・・・
 　　なんだよ、その泊まっていくって</t>
         </is>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>ん・・・っと
 　　目の前に・・・・リボンの付いた
@@ -1950,8 +1621,8 @@
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+    <row r="149">
+      <c r="A149" t="inlineStr">
         <is>
           <t>そう言って胸元の
 リボンをフリフリと振って
@@ -1959,8 +1630,8 @@
         </is>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>久遠が言ってる
 泊まるって意味は
@@ -1968,16 +1639,16 @@
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>流石に即答で
 良いとは言えない俺・・・</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>・・・久遠・・・お前・・・
 　　自分の言ってる意味
@@ -1985,8 +1656,8 @@
         </is>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>それに・・・
 　　俺のトコ泊まるって
@@ -1994,55 +1665,55 @@
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>泊まるって・・・
 　　えっちするって事だよ</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+    <row r="155">
+      <c r="A155" t="inlineStr">
         <is>
           <t>久遠ははっきりと明言する</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
+    <row r="156">
+      <c r="A156" t="inlineStr">
         <is>
           <t>すると逆にこっちが
 言い出しにくくなってしまった</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>俺だって久遠の行為は嬉しいし・・・
 出来れば受け入れたい</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>それだけ今の俺には
 久遠に対する想いが募っていた</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="159">
+      <c r="A159" t="inlineStr">
         <is>
           <t>身近な大切な女の子って
 いうよりも</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="160">
+      <c r="A160" t="inlineStr">
         <is>
           <t>無くてはならない女の子に
 なりつつあるって
@@ -2050,8 +1721,8 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>でも、その反面
 もう少しゆっくり時間をかけたい
@@ -2059,24 +1730,24 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>素直に久遠を受け入れられない
 原因の一つでもあった</t>
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>俺・・・久遠には
 　　色々と感謝してる・・・</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>お前の気持ちも嬉しいし
 　　受け入れたい・・・
@@ -2084,8 +1755,8 @@
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>俺がやっと考えをまとめ
 久遠になんとか今の自分の複雑な
@@ -2093,8 +1764,8 @@
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>すると久遠は俺を
 両手で包み込む様に抱いて
@@ -2102,8 +1773,8 @@
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>お兄ちゃん・・恋愛はね
 　　一瞬で燃え上がるものなんだよ
@@ -2111,8 +1782,8 @@
         </is>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+    <row r="168">
+      <c r="A168" t="inlineStr">
         <is>
           <t>ボクとお兄ちゃんが
 　　その一瞬を大事にして
@@ -2120,8 +1791,8 @@
         </is>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>ば・・馬〜〜鹿・・・
 　　なにお前そんな
@@ -2129,16 +1800,16 @@
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
+    <row r="170">
+      <c r="A170" t="inlineStr">
         <is>
           <t>俺は久遠を茶化す様に
 言ってはみるものの</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>久遠のその言葉に
 自分の言い訳がましい
@@ -2146,8 +1817,8 @@
         </is>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>へへっ・・・これ
 　　前にお兄ちゃんがボクに言った
@@ -2155,16 +1826,16 @@
         </is>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>えっ・・・？
 　　俺が・・そんな事・・・</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>あ・・えと・・・
 　　そのうち言うというか・・・
@@ -2172,39 +1843,39 @@
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>あっそうそう・・・夢の中で
 　　お兄ちゃんがボクに言ったんだよ</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>夢・・・ねぇ・・・</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>そう言って甘える様に
 俺の胸元に抱きついてくる久遠</t>
         </is>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>俺はその久遠に手を回して
 抱き寄せた・・・</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>・・・さっきも言ったよね
 　　プレゼントなんて
@@ -2212,8 +1883,8 @@
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>ボクが欲しいのは
 　　これから作っていくお兄ちゃんとの
@@ -2221,38 +1892,38 @@
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
+    <row r="181">
+      <c r="A181" t="inlineStr">
         <is>
           <t>馬鹿・・・</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>もう・・・忘れちゃった
 　　何度この台詞を言ったのか・・・</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>ボソボソと呟く久遠</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>俺はそんな久遠の頭を撫でると
 久遠の耳元で囁く</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>もういいよ・・久遠・・・
 　　あんま久遠にリードされると
@@ -2260,8 +1931,8 @@
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>そう言って、主導権を握るかの様に
 俺は久遠を抱き寄せ
@@ -2269,8 +1940,8 @@
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>へへ・・・お兄ちゃん・・・
 　　お兄ちゃんがまだ迷うなら・・・
@@ -2278,15 +1949,15 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>・・・考えておく</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+    <row r="189">
+      <c r="A189" t="inlineStr">
         <is>
           <t>・・・そう言いながら俺は
 久遠をギュッと抱き締めると
@@ -2294,8 +1965,8 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+    <row r="190">
+      <c r="A190" t="inlineStr">
         <is>
           <t>少し薄暗いけど
 はっきりと分かる
@@ -2303,16 +1974,16 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>俺が思っていたよりも
 ずっと女性的で</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+    <row r="192">
+      <c r="A192" t="inlineStr">
         <is>
           <t>うっすらと隙間から差し込む
 雪明かりが久遠のあどけない
@@ -2320,31 +1991,31 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>久遠・・・・・
 　　綺麗だな・・・</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>クスッ
 　　・・・・・もっと言って・・・</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>綺麗だ・・・</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="196">
+      <c r="A196" t="inlineStr">
         <is>
           <t>他に洒落た言葉も見付からず
 俺は、久遠の下着をまさぐりながら
@@ -2352,15 +2023,15 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+    <row r="197">
+      <c r="A197" t="inlineStr">
         <is>
           <t>・・・・んっ・・・</t>
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+    <row r="198">
+      <c r="A198" t="inlineStr">
         <is>
           <t>何度もＫｉｓｓを交わし
 そして久遠の体を確認する様に
@@ -2368,8 +2039,8 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+    <row r="199">
+      <c r="A199" t="inlineStr">
         <is>
           <t>そして久遠を
 少し抱き上げる様にして
@@ -2377,62 +2048,62 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>あ・・ちょっとまって
 　　・・・お兄ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+    <row r="201">
+      <c r="A201" t="inlineStr">
         <is>
           <t>俺が久遠の淡い茂みに
 手を伸ばそうとすると</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+    <row r="202">
+      <c r="A202" t="inlineStr">
         <is>
           <t>久遠は少し上気した
 顔で俺に優しくＫｉｓｓをした</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>どした・・・？</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>俺がそう尋ねると
 久遠は軽く首を横に振って答えた</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>へへっ・・・
 　　ボクだけ裸なんてズルだよ</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>なんだよ・・ズルって・・・</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>まぁまぁ・・・
 　　今度はボクが
@@ -2440,8 +2111,8 @@
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+    <row r="208">
+      <c r="A208" t="inlineStr">
         <is>
           <t>いいから・・・
 　　お兄ちゃんはそのまま
@@ -2449,8 +2120,8 @@
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 俺にひざまずく格好で
@@ -2458,8 +2129,8 @@
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>そして、久遠の様子を見守っていると
 久遠は俺のトランクスを下げ
@@ -2467,15 +2138,15 @@
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>おい、久遠？</t>
         </is>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+    <row r="212">
+      <c r="A212" t="inlineStr">
         <is>
           <t>てっきり脱がすものかと
 ばかり思っていた俺は
@@ -2483,31 +2154,31 @@
         </is>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>でも久遠はペロッと舌を出しながら
 俺の顔を見上げて言った</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
+    <row r="214">
+      <c r="A214" t="inlineStr">
         <is>
           <t>しばらくボクに任せてて・・・
 　　お兄ちゃんの綺麗にしたげる・・・</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+    <row r="215">
+      <c r="A215" t="inlineStr">
         <is>
           <t>ペチャ・・ペチャ・・・</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 まるでアイスかなにかを
@@ -2515,8 +2186,8 @@
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>俺のモノを
 細い指先と小さな舌で
@@ -2524,16 +2195,16 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>既に充血しきっていた
 俺のモノには</t>
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
+    <row r="219">
+      <c r="A219" t="inlineStr">
         <is>
           <t>久遠の舌と指が動く度に
 なんとも言えない快感が
@@ -2541,54 +2212,54 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>ペチャ・・・ペチャ・・・</t>
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
+    <row r="221">
+      <c r="A221" t="inlineStr">
         <is>
           <t>久遠・・・そろそろ・・・</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+    <row r="222">
+      <c r="A222" t="inlineStr">
         <is>
           <t>俺は込み上げてくる物に
 耐えられそうも無く</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>我慢出来なくなる前に
 久遠に止めさせようとする</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+    <row r="224">
+      <c r="A224" t="inlineStr">
         <is>
           <t>んっ・・・いいよ・・・
 　　ボクの口で出して・・・</t>
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
+    <row r="225">
+      <c r="A225" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 止めるどころか</t>
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+    <row r="226">
+      <c r="A226" t="inlineStr">
         <is>
           <t>さっきよりも
 明らかに激しく
@@ -2596,8 +2267,8 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>ペチャ・・ペチャ・・
 ペチャ・・ペチャ・・
@@ -2605,53 +2276,53 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>う・・・久遠・・・</t>
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>久遠の指先や舌の動きは
 絶妙に俺のモノを刺激し</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>俺も思わず
 我慢し切れなくなる</t>
         </is>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
+    <row r="231">
+      <c r="A231" t="inlineStr">
         <is>
           <t>久遠・・久遠！！</t>
         </is>
       </c>
     </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
+    <row r="232">
+      <c r="A232" t="inlineStr">
         <is>
           <t>ドクッドクッドクッ・・・</t>
         </is>
       </c>
     </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
+    <row r="233">
+      <c r="A233" t="inlineStr">
         <is>
           <t>久遠は俺がイクのを
 見計らったのか</t>
         </is>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>俺のモノを小さな口で
 くわえ込み、そして俺の白濁液を
@@ -2659,46 +2330,46 @@
         </is>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>コクン・・・</t>
         </is>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>はぁ・・はぁ・・はぁ・・・</t>
         </is>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>へへっ・・・
 　　ちゃんと綺麗にするからね</t>
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>久遠は俺の白濁液を
 飲み込んだかと思うと</t>
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>俺のモノを
 ストローみたいに吸ったり</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>軽く手でしごいてはまだ
 残っていた白濁液を
@@ -2706,24 +2377,24 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>はぁ・・はぁ・・・久遠・・・
 　　どこで・・そんなの覚えたんだ・・・</t>
         </is>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>俺・・・久遠は
 　　こういうの初めてかと思ってた</t>
         </is>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>多少・・・というか
 やっぱり動揺みたいな物は
@@ -2731,8 +2402,8 @@
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>日頃の久遠は
 ちょっと子供っぽいし
@@ -2740,16 +2411,16 @@
         </is>
       </c>
     </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
+    <row r="245">
+      <c r="A245" t="inlineStr">
         <is>
           <t>だから、えっちとかそういうのは
 全然無縁だと思っていたからだ</t>
         </is>
       </c>
     </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>でも久遠は
 俺の服を脱がし始めると
@@ -2757,8 +2428,8 @@
         </is>
       </c>
     </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>へっ・・・？
 　　ボク・・・バージンだよ
@@ -2766,8 +2437,8 @@
         </is>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
+    <row r="248">
+      <c r="A248" t="inlineStr">
         <is>
           <t>あ・・いやさ・・・
 　　なんか結構手慣れてるし・・・
@@ -2775,8 +2446,8 @@
         </is>
       </c>
     </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
+    <row r="249">
+      <c r="A249" t="inlineStr">
         <is>
           <t>ふぇふぇふぇ
 　　みんなお兄ちゃんが
@@ -2784,30 +2455,30 @@
         </is>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
+    <row r="250">
+      <c r="A250" t="inlineStr">
         <is>
           <t>お兄ちゃん、えっちになると
 　　結構うるさかったし・・・</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
+    <row r="251">
+      <c r="A251" t="inlineStr">
         <is>
           <t>え？？</t>
         </is>
       </c>
     </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>お・・俺・・？？？</t>
         </is>
       </c>
     </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
+    <row r="253">
+      <c r="A253" t="inlineStr">
         <is>
           <t>・・・俺・・・
 久遠にそんな事
@@ -2815,16 +2486,16 @@
         </is>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
+    <row r="254">
+      <c r="A254" t="inlineStr">
         <is>
           <t>思わず頭の中で色々と
 回想するけど、全く心当たりが無い</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+    <row r="255">
+      <c r="A255" t="inlineStr">
         <is>
           <t>もしかして俺の部屋の
 掃除がてらにエロ本でも
@@ -2832,38 +2503,38 @@
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+    <row r="256">
+      <c r="A256" t="inlineStr">
         <is>
           <t>あっ・・・ま・・まぁ・・・・
 　　夢で・・・教わったっていうか・・・</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>ゆ・・・夢・・・</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>へへっ・・・
 　　気にしない気にしない</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>ＣＨＵ！</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
+    <row r="260">
+      <c r="A260" t="inlineStr">
         <is>
           <t>そう言って久遠は
 俺に抱きつきながら
@@ -2871,8 +2542,8 @@
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
+    <row r="261">
+      <c r="A261" t="inlineStr">
         <is>
           <t>俺は入ってくる
 久遠の舌に自分の舌を
@@ -2880,31 +2551,31 @@
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>そっと久遠の下半身に
 手を伸ばし始めた・・・</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>んっ・・・ボクのは・・・
 　　もう平気だよ・・・</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>俺が久遠のそこに触れると</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+    <row r="265">
+      <c r="A265" t="inlineStr">
         <is>
           <t>久遠の言う通りに
 茂みが濡れてるのが分かる程
@@ -2912,46 +2583,46 @@
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
+    <row r="266">
+      <c r="A266" t="inlineStr">
         <is>
           <t>・・・クスッ・・・
 　　フェラで濡れた？</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>もう、デリカシー無いよ！</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>カプッ</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>久遠はいきなり顔を真っ赤にして
 俺の耳たぶを軽くかじった</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>痛っ！
 　　・・・こらっ久遠</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="271">
+      <c r="A271" t="inlineStr">
         <is>
           <t>俺は久遠のお尻に手を回すと
 膝の上に抱え込む様にして
@@ -2959,8 +2630,8 @@
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="272">
+      <c r="A272" t="inlineStr">
         <is>
           <t>そして、既に復活していた
 俺のモノを
@@ -2968,15 +2639,15 @@
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="273">
+      <c r="A273" t="inlineStr">
         <is>
           <t>あ・・あややっ・・・</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>いきなりひょいっと
 抱えあげられた久遠は
@@ -2984,16 +2655,16 @@
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>俺はそんな久遠に
 軽くＫｉｓｓをすると</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
+    <row r="276">
+      <c r="A276" t="inlineStr">
         <is>
           <t>久遠を俺の上に
 座らせる様にして
@@ -3001,22 +2672,22 @@
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="277">
+      <c r="A277" t="inlineStr">
         <is>
           <t>きつっ・・・</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
+    <row r="278">
+      <c r="A278" t="inlineStr">
         <is>
           <t>い・・痛いっ！！</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+    <row r="279">
+      <c r="A279" t="inlineStr">
         <is>
           <t>も、もうっ！
 　　ボク、バージンだって
@@ -3024,8 +2695,8 @@
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
+    <row r="280">
+      <c r="A280" t="inlineStr">
         <is>
           <t>久遠は逃げる様に
 シーツを掴んで
@@ -3033,8 +2704,8 @@
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="281">
+      <c r="A281" t="inlineStr">
         <is>
           <t>俺は久遠のお尻を手で固定して
 久遠を抱き寄せる様にしながら
@@ -3042,24 +2713,24 @@
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+    <row r="282">
+      <c r="A282" t="inlineStr">
         <is>
           <t>久遠は体を丸める様にして
 痛みを堪えている</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
+    <row r="283">
+      <c r="A283" t="inlineStr">
         <is>
           <t>さっきまでの手慣れた感じとは
 打って変わって</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+    <row r="284">
+      <c r="A284" t="inlineStr">
         <is>
           <t>俺にされるがままに
 ただ体を強ばらせている
@@ -3067,48 +2738,48 @@
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
+    <row r="285">
+      <c r="A285" t="inlineStr">
         <is>
           <t>俺は久遠の頭を優しく撫でると
 久遠をゆっくりと突き上げ始める</t>
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
+    <row r="286">
+      <c r="A286" t="inlineStr">
         <is>
           <t>すると久遠は眉間に
 少し皺を寄せて</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
+    <row r="287">
+      <c r="A287" t="inlineStr">
         <is>
           <t>ギュッとシーツにしがみついて
 じっと動かなくなる</t>
         </is>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
+    <row r="288">
+      <c r="A288" t="inlineStr">
         <is>
           <t>久遠が体をグッと丸めるので
 やりにくくなった俺は</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+    <row r="289">
+      <c r="A289" t="inlineStr">
         <is>
           <t>久遠のお尻を軽く持ち上げて
 無理矢理突き挿れる体勢になる</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
+    <row r="290">
+      <c r="A290" t="inlineStr">
         <is>
           <t>あぅ・・・・
 　　お・・お兄ちゃん
@@ -3116,8 +2787,8 @@
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="291">
+      <c r="A291" t="inlineStr">
         <is>
           <t>しばらくは我慢していた久遠も
 かなり痛いのか思わず力も抜けて
@@ -3125,8 +2796,8 @@
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
+    <row r="292">
+      <c r="A292" t="inlineStr">
         <is>
           <t>すると俺も、自分の快楽が優先になり
 久遠の言葉も聞こえないフリをしながら
@@ -3134,70 +2805,70 @@
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="293">
+      <c r="A293" t="inlineStr">
         <is>
           <t>ば・・ばかぁ・・・
 　　ホントに痛いよぉ・・・</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="294">
+      <c r="A294" t="inlineStr">
         <is>
           <t>・・・久遠
 　　もうちょっとだから・・・</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="295">
+      <c r="A295" t="inlineStr">
         <is>
           <t>ん・・・んくっ</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="296">
+      <c r="A296" t="inlineStr">
         <is>
           <t>俺は久遠の抗議の声も
 Ｋｉｓｓで誤魔化しながら</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="297">
+      <c r="A297" t="inlineStr">
         <is>
           <t>自分の中に込み上げてくる物を
 感じ始めてきた</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
+    <row r="298">
+      <c r="A298" t="inlineStr">
         <is>
           <t>あう・・ちょ・・
 　　ちょっとだけタンマ</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>そう言うと久遠は俺の体を突き倒して
 ベッドの反対側に逃げようとする</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>あ、久遠！</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>思わず逃げる久遠を抱きかかえると
 俺は久遠をぎゅっとベッドに
@@ -3205,37 +2876,37 @@
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>久遠・・・もう少しだから</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>う・・ううぅ・・・</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>俺はまだ抜けて間もないモノを
 また元の場所にすっぽりと納める</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>く・・・・んっ・・・</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>すると久遠はもう観念したのか
 そのまま力が抜けた様に
@@ -3243,16 +2914,16 @@
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>俺はそんな久遠の様子に
 少し心が痛むものの</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>もう少しでイキそうな感覚が
 どうしても優先して
@@ -3260,31 +2931,31 @@
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>ハァハァハァ・・・久遠・・・・
 　　もう少しだから・・・</t>
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>んぐっ・・んん・・んん・・・</t>
         </is>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>久遠はシーツを噛みながら
 声を殺して俺の限界を待つ</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>俺は自分の込み上げてくる感覚に
 任せてリズミカルに
@@ -3292,15 +2963,15 @@
         </is>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>あ・・ああ・・あああっ</t>
         </is>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>俺の動きが大きく早くなる度に
 久遠は体を仰け反らせ
@@ -3308,38 +2979,38 @@
         </is>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>そして、俺も限界の時を迎える</t>
         </is>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>ハァハァハァハァ・・・
 　　うっ・・・ううっ！</t>
         </is>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>んんっ！</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>う〜〜〜っ
 　　・・・まだ痛いよぉ</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>久遠はわざと俺に聞こえる様に
 自分の下腹を押さえながら
@@ -3347,15 +3018,15 @@
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>ん・・だから悪かったって・・・</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>俺は久遠を軽く抱き寄せて
 謝るけど久遠はぷいっと
@@ -3363,8 +3034,8 @@
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>お兄ちゃんがあんなに
 　　激しくするから
@@ -3372,8 +3043,8 @@
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>お・・おいおい・・・
 　　まぁ・・・それだけ
@@ -3381,8 +3052,8 @@
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>お兄ちゃんは良くても・・・
 　　もう、ボク赤ちゃんも
@@ -3390,8 +3061,8 @@
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>・・・・・・久遠・・・・・
 　　ホントはなにが言いたいんだよ
@@ -3399,31 +3070,31 @@
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>えっ！？</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>い・・・
 　　痛いよぉぉぉ</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>・・・お前・・・なんか俺に
 　　頼みたい事でもあるんだろ・・・</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>言いにくい事あると
 　　いっつも同じ様な事しやがって・・・
@@ -3431,48 +3102,48 @@
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>俺はそう言って
 久遠の頭をコツンと叩くと</t>
         </is>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>久遠は少し苦笑しながら
 話し出した・・・</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>へ・・へへへっ
 　　ん・・と・・ね・・・</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>やっぱり・・・ほら
 　　・・・クリスマスだし・・・</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>ここら辺に着ける物とか
 　　欲しいかなぁ・・・とか</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>そう言って久遠は
 左手の薬指をくねくねさせて
@@ -3480,23 +3151,23 @@
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>はぁ・・・
 　　・・・・・・ほれ</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="337">
+      <c r="A337" t="inlineStr">
         <is>
           <t>わ〜い♪</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="338">
+      <c r="A338" t="inlineStr">
         <is>
           <t>俺はなかなか渡す機会の無かった
 例の指輪を取り出すと
@@ -3504,8 +3175,8 @@
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="339">
+      <c r="A339" t="inlineStr">
         <is>
           <t>すると久遠はそれがなんなのか
 分かっているかの様に
@@ -3513,22 +3184,22 @@
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="340">
+      <c r="A340" t="inlineStr">
         <is>
           <t>指輪を自分の薬指に通した</t>
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
+    <row r="341">
+      <c r="A341" t="inlineStr">
         <is>
           <t>ふんふん♪</t>
         </is>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
+    <row r="342">
+      <c r="A342" t="inlineStr">
         <is>
           <t>・・・お・・おい・・・
 　　なんか・・・リアクション
@@ -3536,16 +3207,16 @@
         </is>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
+    <row r="343">
+      <c r="A343" t="inlineStr">
         <is>
           <t>・・・ほ・・ほら・・・
 　　あれだけ欲しがってた訳だし</t>
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="344">
+      <c r="A344" t="inlineStr">
         <is>
           <t>・・・一応俺も
 　　驚かせようと思ってたんだが・・・
@@ -3553,47 +3224,47 @@
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
+    <row r="345">
+      <c r="A345" t="inlineStr">
         <is>
           <t>ん・・ん・・・
 　　ほら・・・なんていうか・・・</t>
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="346">
+      <c r="A346" t="inlineStr">
         <is>
           <t>びっくりし過ぎて
 　　気が動転してたというか・・・</t>
         </is>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>あんまり細かい事は
 　　気にしちゃ駄目だよ♪</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
+    <row r="348">
+      <c r="A348" t="inlineStr">
         <is>
           <t>ＣＨＵ！</t>
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>なんか久遠に丸め込まれた
 気がするが・・・</t>
         </is>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>久遠が大事そうに
 指輪を見つめているのを見て
@@ -3601,16 +3272,16 @@
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>・・・へへ♪
 　　届いちゃってたりして・・・</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>すると久遠は
 指輪のはまった左手で
@@ -3618,22 +3289,22 @@
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>・・・なにが？</t>
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>内緒♪</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 じ〜っと俺の事を見上げながら
@@ -3641,30 +3312,30 @@
         </is>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>お・・おい久遠・・・</t>
         </is>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>ねね♪
 　　もいっかい、えっちしよ♪</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>いっ？</t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>だって・・・ボクばっかり痛くって
 　　ぜんぜん良くなかったもん
@@ -3672,39 +3343,39 @@
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>だから・・・早くボクも
 　　良くなる様に・・・ねっ♪</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>ま、待った・・・俺は
 　　結局２回してる訳だし・・・</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>ちょ、ちょっと待てって！！</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>駄目だもん♪
 　　ＣＨＵ！ＣＨＵ！</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>そして、久遠は止めさせようとする
 俺に強引にのしかかると
@@ -3712,31 +3383,24 @@
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>昨日はあれから
 マヂで殺されるかと思った</t>
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>少しずつ良くは
 なってるみたいなんだけど</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>最後までイク事が
 出来なかった久遠は
@@ -3744,16 +3408,16 @@
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>結局、朝まで・・・
 まさに吸い尽くされたって感じだ</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>それでも昼過ぎに起きると
 何事も無かったかの様な姿は
@@ -3761,23 +3425,23 @@
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>お兄ちゃん、早く早く♪</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>久遠はそう言うと
 絡めた腕を引っ張りながら</t>
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>ふらふらしてる俺を
 久遠のお勧めとかいう
@@ -3785,8 +3449,8 @@
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>う゛〜・・・
 　　ちょっと手加減しろって
@@ -3794,22 +3458,22 @@
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>もぉ・・・だらしないぞ〜</t>
         </is>
       </c>
     </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>だ、誰のせいだ</t>
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>あ・・そうだ
 　　お兄ちゃん、指輪にメッセージ
@@ -3817,23 +3481,23 @@
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>・・・ん？
 　　いいけど、なんて彫るんだ？</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>ん・・・内緒</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>俺は久遠の見せた笑顔に
 思わず目を背けながら
@@ -3841,8 +3505,8 @@
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>一瞬だけど
 その久遠の表情を
@@ -3850,8 +3514,8 @@
         </is>
       </c>
     </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="381">
+      <c r="A381" t="inlineStr">
         <is>
           <t>うん♪
 　　それじゃちょっと
@@ -3859,24 +3523,24 @@
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="382">
+      <c r="A382" t="inlineStr">
         <is>
           <t>って、おい
 　　飯行くんじゃないのか〜？</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="383">
+      <c r="A383" t="inlineStr">
         <is>
           <t>久遠は
 俺に振り返る事無く</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="384">
+      <c r="A384" t="inlineStr">
         <is>
           <t>真っ先に、この前の
 アクセサリー屋に
@@ -3884,23 +3548,16 @@
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="385">
+      <c r="A385" t="inlineStr">
         <is>
           <t>俺は久遠の後を追いかける様に
 ゆっくりと歩き出した・・・</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
+    <row r="386">
+      <c r="A386" t="inlineStr">
         <is>
           <t>ふと思い返せば
 もう・・あれから・・・
@@ -3908,8 +3565,8 @@
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
+    <row r="387">
+      <c r="A387" t="inlineStr">
         <is>
           <t>でも、俺と久遠の時間は
 あっという間に色々な思い出に
@@ -3917,24 +3574,24 @@
         </is>
       </c>
     </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
+    <row r="388">
+      <c r="A388" t="inlineStr">
         <is>
           <t>久遠・・・
 　　もう起きてていいのか？</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
+    <row r="389">
+      <c r="A389" t="inlineStr">
         <is>
           <t>あれからの俺と久遠は
 若さに身を任せたというか・・・</t>
         </is>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>俺が卒業するとそのまま
 アパートを貸りて、そこに久遠が
@@ -3942,16 +3599,16 @@
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
+    <row r="391">
+      <c r="A391" t="inlineStr">
         <is>
           <t>結構ありがちな
 同棲生活を送っていた</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="392">
+      <c r="A392" t="inlineStr">
         <is>
           <t>そして、１年程前には
 久遠の成人の祝いだとか言って
@@ -3959,16 +3616,16 @@
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
+    <row r="393">
+      <c r="A393" t="inlineStr">
         <is>
           <t>同棲については黙っていた
 放任主義の俺と久遠の両親も</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
+    <row r="394">
+      <c r="A394" t="inlineStr">
         <is>
           <t>流石にこの時だけは
 黙っておらず
@@ -3976,16 +3633,16 @@
         </is>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
+    <row r="395">
+      <c r="A395" t="inlineStr">
         <is>
           <t>そのうち
 久遠に子供が出来たのが分かると</t>
         </is>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
+    <row r="396">
+      <c r="A396" t="inlineStr">
         <is>
           <t>手の平を返した様に
 大人しくなり、既に孫の話で
@@ -3993,8 +3650,8 @@
         </is>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="397">
+      <c r="A397" t="inlineStr">
         <is>
           <t>その・・・俺達の子供なんだけど
 今はまだ久遠のお腹にいて
@@ -4002,80 +3659,80 @@
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t>ん・・・・・
 　　まだ・・・熱下がってないな</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
+    <row r="399">
+      <c r="A399" t="inlineStr">
         <is>
           <t>ほら・・・
 　　駄目だぞ・・・ちゃんと寝てないと</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
+    <row r="400">
+      <c r="A400" t="inlineStr">
         <is>
           <t>少し気怠そうな面もちで
 返事をする久遠・・・</t>
         </is>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
+    <row r="401">
+      <c r="A401" t="inlineStr">
         <is>
           <t>実は、ここ１週間ばかり
 風邪を拗らせてしまい</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
+    <row r="402">
+      <c r="A402" t="inlineStr">
         <is>
           <t>予定日が近い事もあって
 病院に入院させていたのだ</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>あの・・・ね
 　　お兄ちゃん・・・</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>ん？
 　　今日はなんか元気無いな・・・</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
+    <row r="405">
+      <c r="A405" t="inlineStr">
         <is>
           <t>もう、予定日も近いんだし
 　　元気出さないと・・・</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
+    <row r="406">
+      <c r="A406" t="inlineStr">
         <is>
           <t>・・・ボクの話・・・
 　　聞いてくれないかな？</t>
         </is>
       </c>
     </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
+    <row r="407">
+      <c r="A407" t="inlineStr">
         <is>
           <t>話？
 　　なんだ・・・またなにか
@@ -4083,8 +3740,8 @@
         </is>
       </c>
     </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
+    <row r="408">
+      <c r="A408" t="inlineStr">
         <is>
           <t>そうだね・・・
 　　ボクはずっと欲しかった物があるよ
@@ -4092,15 +3749,15 @@
         </is>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>ん？なんだよ・・・それ・・・</t>
         </is>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>言っておくけど
 　　あんまり高い物は
@@ -4108,31 +3765,24 @@
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
+    <row r="411">
+      <c r="A411" t="inlineStr">
         <is>
           <t>ボクが欲しかったのは・・・
 　　たった一つの・・未来・・・</t>
         </is>
       </c>
     </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
+    <row r="412">
+      <c r="A412" t="inlineStr">
         <is>
           <t>久遠がなにを
 言い出しているのか分からない</t>
         </is>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t>熱のせいなのかもしれないけど
 久遠の目は至って真剣で
@@ -4140,8 +3790,8 @@
         </is>
       </c>
     </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・ごめんね・・・
 　　ずっと・・・黙ってた事
@@ -4149,8 +3799,8 @@
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t>はぁ・・・
 　　また俺に内緒で
@@ -4158,24 +3808,24 @@
         </is>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>俺が久遠の頭を
 撫でながらそう言うと</t>
         </is>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>久遠はそっと目を閉じて
 俺に言う・・・</t>
         </is>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>ボクはね・・・明日・・・
 　　赤ちゃん産んで・・・そのまま
@@ -4183,8 +3833,8 @@
         </is>
       </c>
     </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>ジョーク？
 それにしてはこの時期に
@@ -4192,16 +3842,16 @@
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t>俺はちょっとマジになって
 少し強く久遠に言ってしまう</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t>馬鹿！
 　　お前な、冗談でも言って良い事と
@@ -4209,8 +3859,8 @@
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>俺がそう言うと
 久遠は小さく首を横に振って
@@ -4218,47 +3868,47 @@
         </is>
       </c>
     </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t>最後まで・・・・
 　　黙って聞いてお兄ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t>ボクは・・・知ってたんだ・・・
 　　この日が来るの・・・</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t>な・・・なんだよ</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t>前にも予知能力だとか・・・
 　　夢で見たとか言って</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t>何度か、お兄ちゃんの事
 　　驚かせた事・・・あったよね・・・</t>
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
         <is>
           <t>でもね・・・それって
 　　ボクは予知してた訳じゃないんだ・・・
@@ -4266,8 +3916,8 @@
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>おい・・久遠・・・
 　　お前、なに馬鹿な事
@@ -4275,16 +3925,16 @@
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t>お前が死ぬだって？？
 　　この日を知っていたって？？</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t>ボクは・・・何度も
 　　お兄ちゃんに出会って
@@ -4292,31 +3942,24 @@
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t>そして別れていった・・・
 　　また、お兄ちゃんに逢う為に</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t>だから・・・
 　　だからボクは・・・</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t>何度も、何度も
 　　自分の経験した事を利用して
@@ -4324,8 +3967,8 @@
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+    <row r="435">
+      <c r="A435" t="inlineStr">
         <is>
           <t>・・・なのに
 　　・・・どうしても
@@ -4333,15 +3976,15 @@
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t>・・・・・久遠・・・・</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t>ごめんな・・・俺・・・久遠が
 　　なに言ってるのか・・・
@@ -4349,24 +3992,24 @@
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t>う・・うう・・お兄ちゃん・・・
 　　ボク・・ボクはどうしたら・・・</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t>マタニティーブルーって
 ヤツなんだろうか・・・</t>
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t>久遠はポロポロと涙を
 こぼしながら
@@ -4374,32 +4017,32 @@
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t>俺は・・・そんな久遠を
 優しく抱き締めながら</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>久遠の体温を
 いつまでも感じていた・・・</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>ボクは・・・欲しかったんだ
 　　　　たった一つの未来が・・・</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t>お兄ちゃんと・・・
 　　　　生まれてくるあの娘と・・・
@@ -4407,16 +4050,16 @@
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t>・・・・やっぱり・・・
 　　未来は変えられなかった・・・</t>
         </is>
       </c>
     </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t>ボクが気付いた時・・・
 そこはもう・・・
@@ -4424,32 +4067,32 @@
         </is>
       </c>
     </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t>ボクは・・・ここから
 またあの結末の未来まで・・・</t>
         </is>
       </c>
     </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t>一体どれくらい
 繰り返してきたんだろう・・・</t>
         </is>
       </c>
     </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t>変わる事の無い
 結末の未来を・・・</t>
         </is>
       </c>
     </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t>そしてボクは走り出す
 ボクの行く場所は
@@ -4457,8 +4100,8 @@
         </is>
       </c>
     </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t>ボクの中には
 お兄ちゃんとの思い出が
@@ -4466,16 +4109,16 @@
         </is>
       </c>
     </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t>何度も何度も
 同じ未来を繰り返す度に</t>
         </is>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t>一つ一つ輝いていた思い出達が
 ボクの胸をギュッと潰す様に
@@ -4483,16 +4126,16 @@
         </is>
       </c>
     </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
+    <row r="454">
+      <c r="A454" t="inlineStr">
         <is>
           <t>いつもボクに優しくて
 とっても頼りがいがあって・・・</t>
         </is>
       </c>
     </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
+    <row r="455">
+      <c r="A455" t="inlineStr">
         <is>
           <t>お兄ちゃんの良いトコも
 悪いトコもボクが誰よりも
@@ -4500,24 +4143,24 @@
         </is>
       </c>
     </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t>ボクは・・・
 そんなお兄ちゃんを・・・</t>
         </is>
       </c>
     </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t>ふと・・・その時・・・
 ボクの目にお兄ちゃんの姿が映る・・・</t>
         </is>
       </c>
     </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t>もう・・・それだけで
 今まで、いろんな想いが駆けめぐってた
@@ -4525,190 +4168,52 @@
         </is>
       </c>
     </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t>柚、駅の向こうにある「豆」の
 　　　ケーキ好きなんだよね</t>
         </is>
       </c>
     </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
+    <row r="461">
+      <c r="A461" t="inlineStr">
         <is>
           <t>・・・ここは
 喫茶店「豆」</t>
         </is>
       </c>
     </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>・悠・「今日わ」</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>・悠・「あ・・あの・・・
-　　　恋水の靴・・取って欲しいの」</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>・悠・「恋水ったら
-　　　自分の靴投げちゃって
-　　　あの木にかかっちゃったんです」</t>
-        </is>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>・悠・「ありがとうございます」</t>
-        </is>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>・悠・「ありがとうございました
-　　　それでは失礼いたします」</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>・悠・「すご〜い！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>・悠・「大人ってああやって
-　　　お仕置きするの？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>・悠・「ふ〜ん・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>・悠・「は〜い♪」</t>
-        </is>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
+    <row r="462">
+      <c r="A462" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t>御幸？</t>
         </is>
       </c>
     </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t>「ありがとう」って・・・</t>
         </is>
       </c>
     </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>震える声で・・・
 　　ただ・・・私を見つめて・・・
@@ -4716,158 +4221,84 @@
         </is>
       </c>
     </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t>春菜？</t>
         </is>
       </c>
     </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>・千尋・「健治君！！
-　　　私の事好きだって
-　　　言ったじゃない！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>千尋「こ・・このぉ〜！
-　　浮気者〜〜！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>・咲夜・「うぇぇぇぇん
-　　　先生、怖いですぅ〜」</t>
-        </is>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t>柚！！！</t>
         </is>
       </c>
     </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t>ふんふん♪</t>
         </is>
       </c>
     </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t>ん・・・・・
 　　まだ・・・熱下がってないな</t>
         </is>
       </c>
     </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
+    <row r="471">
+      <c r="A471" t="inlineStr">
         <is>
           <t>ほら・・・
 　　駄目だぞ・・・ちゃんと寝てないと</t>
         </is>
       </c>
     </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
+    <row r="472">
+      <c r="A472" t="inlineStr">
         <is>
           <t>あの・・・ね
 　　お兄ちゃん・・・</t>
         </is>
       </c>
     </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t>ん？
 　　今日はなんか元気無いな・・・</t>
         </is>
       </c>
     </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>もう、予定日も近いんだし
 　　元気出さないと・・・</t>
         </is>
       </c>
     </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>・・・ボクの話・・・
 　　聞いてくれないかな？</t>
         </is>
       </c>
     </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t>話？
 　　なんだ・・・またなにか
@@ -4875,8 +4306,8 @@
         </is>
       </c>
     </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t>そうだね・・・
 　　ボクはずっと欲しかった物があるよ
@@ -4884,15 +4315,15 @@
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t>ん？なんだよ・・・それ・・・</t>
         </is>
       </c>
     </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>言っておくけど
 　　あんまり高い物は
@@ -4900,23 +4331,16 @@
         </is>
       </c>
     </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>ボクが欲しかったのは・・・
 　　たった一つの・・未来・・・</t>
         </is>
       </c>
     </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・ごめんね・・・
 　　ずっと・・・黙ってた事
@@ -4924,8 +4348,8 @@
         </is>
       </c>
     </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>ボクはね・・・明日・・・
 　　赤ちゃん産んで・・・そのまま
@@ -4933,8 +4357,8 @@
         </is>
       </c>
     </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>馬鹿！
 　　お前な、冗談でも言って良い事と
@@ -4942,47 +4366,47 @@
         </is>
       </c>
     </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>最後まで・・・・
 　　黙って聞いてお兄ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>ボクは・・・知ってたんだ・・・
 　　この日が来るの・・・</t>
         </is>
       </c>
     </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>な・・・なんだよ</t>
         </is>
       </c>
     </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>前にも予知能力だとか・・・
 　　夢で見たとか言って</t>
         </is>
       </c>
     </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
+    <row r="488">
+      <c r="A488" t="inlineStr">
         <is>
           <t>何度か、お兄ちゃんの事
 　　驚かせた事・・・あったよね・・・</t>
         </is>
       </c>
     </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
+    <row r="489">
+      <c r="A489" t="inlineStr">
         <is>
           <t>でもね・・・それって
 　　ボクは予知してた訳じゃないんだ・・・
@@ -4990,16 +4414,16 @@
         </is>
       </c>
     </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
+    <row r="490">
+      <c r="A490" t="inlineStr">
         <is>
           <t>お前が死ぬだって？？
 　　この日を知っていたって？？</t>
         </is>
       </c>
     </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
+    <row r="491">
+      <c r="A491" t="inlineStr">
         <is>
           <t>ボクは・・・何度も
 　　お兄ちゃんに出会って
@@ -5007,31 +4431,24 @@
         </is>
       </c>
     </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
+    <row r="492">
+      <c r="A492" t="inlineStr">
         <is>
           <t>そして別れていった・・・
 　　また、お兄ちゃんに逢う為に</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
+    <row r="493">
+      <c r="A493" t="inlineStr">
         <is>
           <t>だから・・・
 　　だからボクは・・・</t>
         </is>
       </c>
     </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
+    <row r="494">
+      <c r="A494" t="inlineStr">
         <is>
           <t>何度も、何度も
 　　自分の経験した事を利用して
@@ -5039,8 +4456,8 @@
         </is>
       </c>
     </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
+    <row r="495">
+      <c r="A495" t="inlineStr">
         <is>
           <t>・・・なのに
 　　・・・どうしても
@@ -5048,15 +4465,15 @@
         </is>
       </c>
     </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
+    <row r="496">
+      <c r="A496" t="inlineStr">
         <is>
           <t>・・・・・久遠・・・・</t>
         </is>
       </c>
     </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
+    <row r="497">
+      <c r="A497" t="inlineStr">
         <is>
           <t>ごめんな・・・俺・・・久遠が
 　　なに言ってるのか・・・
@@ -5064,100 +4481,37 @@
         </is>
       </c>
     </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
+    <row r="498">
+      <c r="A498" t="inlineStr">
         <is>
           <t>う・・うう・・お兄ちゃん・・・
 　　ボク・・ボクはどうしたら・・・</t>
         </is>
       </c>
     </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>猫祐二「にゃ〜♪」</t>
-        </is>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>猫祐二「ふぎゃ！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
+    <row r="499">
+      <c r="A499" t="inlineStr">
         <is>
           <t>祐二？</t>
         </is>
       </c>
     </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="500">
+      <c r="A500" t="inlineStr">
         <is>
           <t>祐里子？？</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
+    <row r="501">
+      <c r="A501" t="inlineStr">
         <is>
           <t>「げっ」ってなんだよ・・・</t>
         </is>
       </c>
     </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
+    <row r="502">
+      <c r="A502" t="inlineStr">
         <is>
           <t>私がね、なにかちょっと失敗したり
 　　　祐里子ちゃんの機嫌を損ねたりすると
@@ -5165,8 +4519,8 @@
         </is>
       </c>
     </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
+    <row r="503">
+      <c r="A503" t="inlineStr">
         <is>
           <t>ああ、この娘、ボクの友達
 　　「如月 刹那」（きさらぎ せつな）
@@ -5174,44 +4528,23 @@
         </is>
       </c>
     </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
+    <row r="504">
+      <c r="A504" t="inlineStr">
         <is>
           <t>こら！町中で
 　　「草薙」を振り回すな！</t>
         </is>
       </c>
     </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
+    <row r="505">
+      <c r="A505" t="inlineStr">
         <is>
           <t>馬鹿・・・</t>
         </is>
       </c>
     </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
+    <row r="506">
+      <c r="A506" t="inlineStr">
         <is>
           <t>もぉ！刀と一緒にするなぁ
 　　これは「草薙」って言って
@@ -5219,29 +4552,15 @@
         </is>
       </c>
     </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
+    <row r="507">
+      <c r="A507" t="inlineStr">
         <is>
           <t>刹那！</t>
         </is>
       </c>
     </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="508">
+      <c r="A508" t="inlineStr">
         <is>
           <t>「ぷっ」って笑ったね・・・
 　　　確かに・・酷いヤツ・・・
@@ -5249,29 +4568,22 @@
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
+    <row r="509">
+      <c r="A509" t="inlineStr">
         <is>
           <t>祐里子！！</t>
         </is>
       </c>
     </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
+    <row r="510">
+      <c r="A510" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
+    <row r="511">
+      <c r="A511" t="inlineStr">
         <is>
           <t>とっさに柚を頼ろうとしたけど
 柚はＰＨＳで一人チャルメラを
@@ -5279,58 +4591,44 @@
         </is>
       </c>
     </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
+    <row r="512">
+      <c r="A512" t="inlineStr">
         <is>
           <t>刹那！</t>
         </is>
       </c>
     </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
+    <row r="513">
+      <c r="A513" t="inlineStr">
         <is>
           <t>刹那！</t>
         </is>
       </c>
     </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
+    <row r="514">
+      <c r="A514" t="inlineStr">
         <is>
           <t>刹那！</t>
         </is>
       </c>
     </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
+    <row r="515">
+      <c r="A515" t="inlineStr">
         <is>
           <t>祐二君♪</t>
         </is>
       </c>
     </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
+    <row r="516">
+      <c r="A516" t="inlineStr">
         <is>
           <t>ちゃんと名前だって
 　　「御幸 春菜」って書いてあったし</t>
         </is>
       </c>
     </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
+    <row r="517">
+      <c r="A517" t="inlineStr">
         <is>
           <t>そうよ！
 　　　私は「御幸 菜摘」（みゆき なつみ）
@@ -5338,239 +4636,85 @@
         </is>
       </c>
     </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>！！！！！！</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
+    <row r="518">
+      <c r="A518" t="inlineStr">
         <is>
           <t>祐二君！</t>
         </is>
       </c>
     </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
+    <row r="519">
+      <c r="A519" t="inlineStr">
         <is>
           <t>祐二君！</t>
         </is>
       </c>
     </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
+    <row r="520">
+      <c r="A520" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
+    <row r="521">
+      <c r="A521" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
+    <row r="522">
+      <c r="A522" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="633">
-      <c r="A633" t="inlineStr">
+    <row r="523">
+      <c r="A523" t="inlineStr">
         <is>
           <t>祐里子？</t>
         </is>
       </c>
     </row>
-    <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>！？</t>
-        </is>
-      </c>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr">
+    <row r="524">
+      <c r="A524" t="inlineStr">
         <is>
           <t>祐二？</t>
         </is>
       </c>
     </row>
-    <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr">
+    <row r="525">
+      <c r="A525" t="inlineStr">
         <is>
           <t>「成敗！」</t>
         </is>
       </c>
     </row>
-    <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="526">
+      <c r="A526" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="527">
+      <c r="A527" t="inlineStr">
         <is>
           <t>柚！！！</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr">
+    <row r="528">
+      <c r="A528" t="inlineStr">
         <is>
           <t>馬鹿・・・</t>
         </is>
       </c>
     </row>
-    <row r="649">
-      <c r="A649" t="inlineStr">
+    <row r="529">
+      <c r="A529" t="inlineStr">
         <is>
           <t>「今日中に帰ってこないと
 ぷれぜんとあげないぞ
@@ -5578,46 +4722,46 @@
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="530">
+      <c r="A530" t="inlineStr">
         <is>
           <t xml:space="preserve">        ｂｙ  ぷりてぃーさんた」</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="531">
+      <c r="A531" t="inlineStr">
         <is>
           <t>玄関に入ると久遠の靴が
 きちんと揃えて置いてある</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="532">
+      <c r="A532" t="inlineStr">
         <is>
           <t>久遠？</t>
         </is>
       </c>
     </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+    <row r="533">
+      <c r="A533" t="inlineStr">
         <is>
           <t>俺は久遠を呼びながら
 リビングへと向かった</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="534">
+      <c r="A534" t="inlineStr">
         <is>
           <t>リビングにも
 久遠はいない・・・</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="535">
+      <c r="A535" t="inlineStr">
         <is>
           <t>久遠のヤツ・・・
 きっとどこかに隠れてて
@@ -5625,24 +4769,24 @@
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="536">
+      <c r="A536" t="inlineStr">
         <is>
           <t>俺はリビングを出ると
 ２階の自分の部屋に向かった</t>
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="537">
+      <c r="A537" t="inlineStr">
         <is>
           <t>おい・・・
 　　久遠・・出てこいよ</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="538">
+      <c r="A538" t="inlineStr">
         <is>
           <t>薄暗い部屋の
 明かりを点けようと手探りで
@@ -5650,63 +4794,63 @@
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="539">
+      <c r="A539" t="inlineStr">
         <is>
           <t>すると突然大きな声と共に
 部屋の明かりが点いた</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="540">
+      <c r="A540" t="inlineStr">
         <is>
           <t>じゃ〜〜ん
 　　サンタさんだぞ♪</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="541">
+      <c r="A541" t="inlineStr">
         <is>
           <t>・・・・・・・久遠</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="542">
+      <c r="A542" t="inlineStr">
         <is>
           <t>突然、サンタの格好（？）で
 久遠が目の前に現れる・・・</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="543">
+      <c r="A543" t="inlineStr">
         <is>
           <t>これが「ぷりてぃーさんた」の
 正体なんだろうか？？</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="544">
+      <c r="A544" t="inlineStr">
         <is>
           <t>・・・どこがサンタだ・・・
 　　サンタは普通おっさんだぞ・・・</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="545">
+      <c r="A545" t="inlineStr">
         <is>
           <t>お前のはコンパニオンって
 　　言うんじゃないのか？</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="546">
+      <c r="A546" t="inlineStr">
         <is>
           <t>ほら・・・よく
 　　クリスマスセールの時に
@@ -5714,8 +4858,8 @@
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="547">
+      <c r="A547" t="inlineStr">
         <is>
           <t>久遠って
 　　誰の事かな？？
@@ -5723,16 +4867,16 @@
         </is>
       </c>
     </row>
-    <row r="668">
-      <c r="A668" t="inlineStr">
+    <row r="548">
+      <c r="A548" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 挑発のつもりなのか</t>
         </is>
       </c>
     </row>
-    <row r="669">
-      <c r="A669" t="inlineStr">
+    <row r="549">
+      <c r="A549" t="inlineStr">
         <is>
           <t>ミニスカートを
 ヒラヒラとさせながら
@@ -5740,16 +4884,16 @@
         </is>
       </c>
     </row>
-    <row r="670">
-      <c r="A670" t="inlineStr">
+    <row r="550">
+      <c r="A550" t="inlineStr">
         <is>
           <t>んじゃ
 　　サンタ、プレゼントくれ・・・</t>
         </is>
       </c>
     </row>
-    <row r="671">
-      <c r="A671" t="inlineStr">
+    <row r="551">
+      <c r="A551" t="inlineStr">
         <is>
           <t>むぅ・・もう
 　　お兄ちゃんって
@@ -5757,48 +4901,48 @@
         </is>
       </c>
     </row>
-    <row r="672">
-      <c r="A672" t="inlineStr">
+    <row r="552">
+      <c r="A552" t="inlineStr">
         <is>
           <t>ボクずっと待ってたのに
 　　・・・こんな時間まで</t>
         </is>
       </c>
     </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
+    <row r="553">
+      <c r="A553" t="inlineStr">
         <is>
           <t>久遠は
 少しすねた顔をすると</t>
         </is>
       </c>
     </row>
-    <row r="674">
-      <c r="A674" t="inlineStr">
+    <row r="554">
+      <c r="A554" t="inlineStr">
         <is>
           <t>あ・・・そういえば
 　　ボクのプレゼントは？？</t>
         </is>
       </c>
     </row>
-    <row r="675">
-      <c r="A675" t="inlineStr">
+    <row r="555">
+      <c r="A555" t="inlineStr">
         <is>
           <t>今日はクリスマスだし・・・
 　　それにボクの誕生日だぞ</t>
         </is>
       </c>
     </row>
-    <row r="676">
-      <c r="A676" t="inlineStr">
+    <row r="556">
+      <c r="A556" t="inlineStr">
         <is>
           <t>・・・サンタは
 　　プレゼントいらんだろ・・・</t>
         </is>
       </c>
     </row>
-    <row r="677">
-      <c r="A677" t="inlineStr">
+    <row r="557">
+      <c r="A557" t="inlineStr">
         <is>
           <t>・・・・・・お兄ちゃん
 　　忘れてたんでしょ・・・
@@ -5806,16 +4950,16 @@
         </is>
       </c>
     </row>
-    <row r="678">
-      <c r="A678" t="inlineStr">
+    <row r="558">
+      <c r="A558" t="inlineStr">
         <is>
           <t>久遠はぷぅと頬を膨らませて
 俺に抗議する・・・</t>
         </is>
       </c>
     </row>
-    <row r="679">
-      <c r="A679" t="inlineStr">
+    <row r="559">
+      <c r="A559" t="inlineStr">
         <is>
           <t>俺もなんか物が物だけに
 ちょっと出すキッカケを
@@ -5823,39 +4967,39 @@
         </is>
       </c>
     </row>
-    <row r="680">
-      <c r="A680" t="inlineStr">
+    <row r="560">
+      <c r="A560" t="inlineStr">
         <is>
           <t>ま・・・まぁ・・・
 　　今度、買いに行くから・・・</t>
         </is>
       </c>
     </row>
-    <row r="681">
-      <c r="A681" t="inlineStr">
+    <row r="561">
+      <c r="A561" t="inlineStr">
         <is>
           <t>ぷぅ・・・</t>
         </is>
       </c>
     </row>
-    <row r="682">
-      <c r="A682" t="inlineStr">
+    <row r="562">
+      <c r="A562" t="inlineStr">
         <is>
           <t>そう言うと久遠は
 別に怒った風でも無く</t>
         </is>
       </c>
     </row>
-    <row r="683">
-      <c r="A683" t="inlineStr">
+    <row r="563">
+      <c r="A563" t="inlineStr">
         <is>
           <t>やれやれといった顔を
 しながら俺に言った</t>
         </is>
       </c>
     </row>
-    <row r="684">
-      <c r="A684" t="inlineStr">
+    <row r="564">
+      <c r="A564" t="inlineStr">
         <is>
           <t>・・・まぁ・・別にいいもん
 　　物なんていつだって
@@ -5863,8 +5007,8 @@
         </is>
       </c>
     </row>
-    <row r="685">
-      <c r="A685" t="inlineStr">
+    <row r="565">
+      <c r="A565" t="inlineStr">
         <is>
           <t>それより、今日は
 　　クリスマスなんだから
@@ -5872,15 +5016,15 @@
         </is>
       </c>
     </row>
-    <row r="686">
-      <c r="A686" t="inlineStr">
+    <row r="566">
+      <c r="A566" t="inlineStr">
         <is>
           <t>思い出？？</t>
         </is>
       </c>
     </row>
-    <row r="687">
-      <c r="A687" t="inlineStr">
+    <row r="567">
+      <c r="A567" t="inlineStr">
         <is>
           <t>へへっ・・・二人だけの
 　　クリスマスパーティー・・・
@@ -5888,8 +5032,8 @@
         </is>
       </c>
     </row>
-    <row r="688">
-      <c r="A688" t="inlineStr">
+    <row r="568">
+      <c r="A568" t="inlineStr">
         <is>
           <t>そう言って久遠は
 ナプキンを被せてある
@@ -5897,8 +5041,8 @@
         </is>
       </c>
     </row>
-    <row r="689">
-      <c r="A689" t="inlineStr">
+    <row r="569">
+      <c r="A569" t="inlineStr">
         <is>
           <t>それじゃ・・・
 　　明かり消して
@@ -5906,8 +5050,8 @@
         </is>
       </c>
     </row>
-    <row r="690">
-      <c r="A690" t="inlineStr">
+    <row r="570">
+      <c r="A570" t="inlineStr">
         <is>
           <t>そうそう
 　　そろそろ雪降るから
@@ -5915,8 +5059,8 @@
         </is>
       </c>
     </row>
-    <row r="691">
-      <c r="A691" t="inlineStr">
+    <row r="571">
+      <c r="A571" t="inlineStr">
         <is>
           <t>はぁ・・・
 　　雪なんて降ってなかったぞ・・・
@@ -5924,95 +5068,95 @@
         </is>
       </c>
     </row>
-    <row r="692">
-      <c r="A692" t="inlineStr">
+    <row r="572">
+      <c r="A572" t="inlineStr">
         <is>
           <t>さっきまで外にいたのだから
 それくらいは流石に分かる</t>
         </is>
       </c>
     </row>
-    <row r="693">
-      <c r="A693" t="inlineStr">
+    <row r="573">
+      <c r="A573" t="inlineStr">
         <is>
           <t>でも、久遠は自信満々の顔で
 俺に言った・・</t>
         </is>
       </c>
     </row>
-    <row r="694">
-      <c r="A694" t="inlineStr">
+    <row r="574">
+      <c r="A574" t="inlineStr">
         <is>
           <t>・・・ボクの予感は
 　　外れないよ・・絶対</t>
         </is>
       </c>
     </row>
-    <row r="695">
-      <c r="A695" t="inlineStr">
+    <row r="575">
+      <c r="A575" t="inlineStr">
         <is>
           <t>俺は久遠の言う通り
 カーテンを開けて外を見る</t>
         </is>
       </c>
     </row>
-    <row r="696">
-      <c r="A696" t="inlineStr">
+    <row r="576">
+      <c r="A576" t="inlineStr">
         <is>
           <t>すると窓の外ではいつの間にか
 深々と雪が降り始めていた</t>
         </is>
       </c>
     </row>
-    <row r="697">
-      <c r="A697" t="inlineStr">
+    <row r="577">
+      <c r="A577" t="inlineStr">
         <is>
           <t>呆気にとられる俺・・・</t>
         </is>
       </c>
     </row>
-    <row r="698">
-      <c r="A698" t="inlineStr">
+    <row r="578">
+      <c r="A578" t="inlineStr">
         <is>
           <t>思わず、今までの久遠との
 やり取りが頭にリフレインする</t>
         </is>
       </c>
     </row>
-    <row r="699">
-      <c r="A699" t="inlineStr">
+    <row r="579">
+      <c r="A579" t="inlineStr">
         <is>
           <t>少し呆然とした俺を
 気にする事も無く</t>
         </is>
       </c>
     </row>
-    <row r="700">
-      <c r="A700" t="inlineStr">
+    <row r="580">
+      <c r="A580" t="inlineStr">
         <is>
           <t>久遠はテーブルに座って
 キャンドルに明かりを灯した</t>
         </is>
       </c>
     </row>
-    <row r="701">
-      <c r="A701" t="inlineStr">
+    <row r="581">
+      <c r="A581" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・
 　　そっち座って・・・</t>
         </is>
       </c>
     </row>
-    <row r="702">
-      <c r="A702" t="inlineStr">
+    <row r="582">
+      <c r="A582" t="inlineStr">
         <is>
           <t>テーブルの上には
 久遠が作ったのか</t>
         </is>
       </c>
     </row>
-    <row r="703">
-      <c r="A703" t="inlineStr">
+    <row r="583">
+      <c r="A583" t="inlineStr">
         <is>
           <t>小さなケーキと
 きれいに彩られた
@@ -6020,16 +5164,16 @@
         </is>
       </c>
     </row>
-    <row r="704">
-      <c r="A704" t="inlineStr">
+    <row r="584">
+      <c r="A584" t="inlineStr">
         <is>
           <t>・・・これ・・・
 　　久遠が全部作ったのか？</t>
         </is>
       </c>
     </row>
-    <row r="705">
-      <c r="A705" t="inlineStr">
+    <row r="585">
+      <c r="A585" t="inlineStr">
         <is>
           <t>・・・へへっ♪
 　　全部、お兄ちゃんが
@@ -6037,16 +5181,16 @@
         </is>
       </c>
     </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
+    <row r="586">
+      <c r="A586" t="inlineStr">
         <is>
           <t>このシャンパンも
 　　探すの大変だったんだから</t>
         </is>
       </c>
     </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
+    <row r="587">
+      <c r="A587" t="inlineStr">
         <is>
           <t>キャンドルの明かりに
 照らされてる久遠は
@@ -6054,32 +5198,32 @@
         </is>
       </c>
     </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
+    <row r="588">
+      <c r="A588" t="inlineStr">
         <is>
           <t>年上の女性の様な雰囲気を
 醸し出している・・・</t>
         </is>
       </c>
     </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
+    <row r="589">
+      <c r="A589" t="inlineStr">
         <is>
           <t>俺はなんだか
 気恥ずかしくなってきて</t>
         </is>
       </c>
     </row>
-    <row r="710">
-      <c r="A710" t="inlineStr">
+    <row r="590">
+      <c r="A590" t="inlineStr">
         <is>
           <t>まともに久遠の顔を見つめる事が
 出来なかった</t>
         </is>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="inlineStr">
+    <row r="591">
+      <c r="A591" t="inlineStr">
         <is>
           <t>・・・好きなって・・・
 　　確かに好きな食い物は揃ってるけど
@@ -6087,15 +5231,15 @@
         </is>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="inlineStr">
+    <row r="592">
+      <c r="A592" t="inlineStr">
         <is>
           <t>えっ・・あ・・・</t>
         </is>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="inlineStr">
+    <row r="593">
+      <c r="A593" t="inlineStr">
         <is>
           <t>ま、まぁ・・・
 　　これから好きになると思うよ
@@ -6103,39 +5247,39 @@
         </is>
       </c>
     </row>
-    <row r="714">
-      <c r="A714" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t>少し言葉を濁しながら
 俺にシャンパンを注ぐ久遠</t>
         </is>
       </c>
     </row>
-    <row r="715">
-      <c r="A715" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t>そして、二つのグラスに
 それが満たされると</t>
         </is>
       </c>
     </row>
-    <row r="716">
-      <c r="A716" t="inlineStr">
+    <row r="596">
+      <c r="A596" t="inlineStr">
         <is>
           <t>久遠は片方のグラスを持って
 俺のグラスに近付けてきた</t>
         </is>
       </c>
     </row>
-    <row r="717">
-      <c r="A717" t="inlineStr">
+    <row r="597">
+      <c r="A597" t="inlineStr">
         <is>
           <t>それじゃ・・・乾杯・・・</t>
         </is>
       </c>
     </row>
-    <row r="718">
-      <c r="A718" t="inlineStr">
+    <row r="598">
+      <c r="A598" t="inlineStr">
         <is>
           <t>グラスを傾ける久遠は
 今まで俺の知っていた
@@ -6143,38 +5287,31 @@
         </is>
       </c>
     </row>
-    <row r="719">
-      <c r="A719" t="inlineStr">
+    <row r="599">
+      <c r="A599" t="inlineStr">
         <is>
           <t>俺は緊張感が漂う雰囲気の中で
 シャンパンを飲み干した</t>
         </is>
       </c>
     </row>
-    <row r="720">
-      <c r="A720" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr">
+    <row r="600">
+      <c r="A600" t="inlineStr">
         <is>
           <t>よいしょっと・・・・</t>
         </is>
       </c>
     </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
+    <row r="601">
+      <c r="A601" t="inlineStr">
         <is>
           <t>久遠はテーブルの上を
 綺麗に片付けると</t>
         </is>
       </c>
     </row>
-    <row r="723">
-      <c r="A723" t="inlineStr">
+    <row r="602">
+      <c r="A602" t="inlineStr">
         <is>
           <t>俺のベッドの上に
 ちょこんと座って
@@ -6182,64 +5319,64 @@
         </is>
       </c>
     </row>
-    <row r="724">
-      <c r="A724" t="inlineStr">
+    <row r="603">
+      <c r="A603" t="inlineStr">
         <is>
           <t>色々と・・・
 　　ありがとな・・・久遠</t>
         </is>
       </c>
     </row>
-    <row r="725">
-      <c r="A725" t="inlineStr">
+    <row r="604">
+      <c r="A604" t="inlineStr">
         <is>
           <t>別に・・・
 　　ボクが好きでやってる事だし</t>
         </is>
       </c>
     </row>
-    <row r="726">
-      <c r="A726" t="inlineStr">
+    <row r="605">
+      <c r="A605" t="inlineStr">
         <is>
           <t>そう言って
 久遠に手を伸ばすと</t>
         </is>
       </c>
     </row>
-    <row r="727">
-      <c r="A727" t="inlineStr">
+    <row r="606">
+      <c r="A606" t="inlineStr">
         <is>
           <t>久遠はその手を
 両手で握り返してくる</t>
         </is>
       </c>
     </row>
-    <row r="728">
-      <c r="A728" t="inlineStr">
+    <row r="607">
+      <c r="A607" t="inlineStr">
         <is>
           <t>へへっ・・・今日は
 　　ここに泊まるって言ってある</t>
         </is>
       </c>
     </row>
-    <row r="729">
-      <c r="A729" t="inlineStr">
+    <row r="608">
+      <c r="A608" t="inlineStr">
         <is>
           <t>だから・・・ボク
 　　今日はここ泊まってく・・・</t>
         </is>
       </c>
     </row>
-    <row r="730">
-      <c r="A730" t="inlineStr">
+    <row r="609">
+      <c r="A609" t="inlineStr">
         <is>
           <t>まだ、ボクの
 　　プレゼントあげてないし</t>
         </is>
       </c>
     </row>
-    <row r="731">
-      <c r="A731" t="inlineStr">
+    <row r="610">
+      <c r="A610" t="inlineStr">
         <is>
           <t>ん・・・っと
 　　目の前に・・・・リボンの付いた
@@ -6247,8 +5384,8 @@
         </is>
       </c>
     </row>
-    <row r="732">
-      <c r="A732" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t>お兄ちゃん・・恋愛はね
 　　一瞬で燃え上がるものなんだよ
@@ -6256,8 +5393,8 @@
         </is>
       </c>
     </row>
-    <row r="733">
-      <c r="A733" t="inlineStr">
+    <row r="612">
+      <c r="A612" t="inlineStr">
         <is>
           <t>ボクとお兄ちゃんが
 　　その一瞬を大事にして
@@ -6265,8 +5402,8 @@
         </is>
       </c>
     </row>
-    <row r="734">
-      <c r="A734" t="inlineStr">
+    <row r="613">
+      <c r="A613" t="inlineStr">
         <is>
           <t>ボクが欲しいのは
 　　これから作っていくお兄ちゃんとの
@@ -6274,32 +5411,32 @@
         </is>
       </c>
     </row>
-    <row r="735">
-      <c r="A735" t="inlineStr">
+    <row r="614">
+      <c r="A614" t="inlineStr">
         <is>
           <t>もう・・・忘れちゃった
 　　何度この台詞を言ったのか・・・</t>
         </is>
       </c>
     </row>
-    <row r="736">
-      <c r="A736" t="inlineStr">
+    <row r="615">
+      <c r="A615" t="inlineStr">
         <is>
           <t>久遠・・・
 　　もう起きてていいのか？</t>
         </is>
       </c>
     </row>
-    <row r="737">
-      <c r="A737" t="inlineStr">
+    <row r="616">
+      <c r="A616" t="inlineStr">
         <is>
           <t>あれからの俺と久遠は
 若さに身を任せたというか・・・</t>
         </is>
       </c>
     </row>
-    <row r="738">
-      <c r="A738" t="inlineStr">
+    <row r="617">
+      <c r="A617" t="inlineStr">
         <is>
           <t>俺が卒業するとそのまま
 アパートを貸りて、そこに久遠が
@@ -6307,16 +5444,16 @@
         </is>
       </c>
     </row>
-    <row r="739">
-      <c r="A739" t="inlineStr">
+    <row r="618">
+      <c r="A618" t="inlineStr">
         <is>
           <t>結構ありがちな
 同棲生活を送っていた</t>
         </is>
       </c>
     </row>
-    <row r="740">
-      <c r="A740" t="inlineStr">
+    <row r="619">
+      <c r="A619" t="inlineStr">
         <is>
           <t>そして、１年程前には
 久遠の成人の祝いだとか言って
@@ -6324,16 +5461,16 @@
         </is>
       </c>
     </row>
-    <row r="741">
-      <c r="A741" t="inlineStr">
+    <row r="620">
+      <c r="A620" t="inlineStr">
         <is>
           <t>同棲については黙っていた
 放任主義の俺と久遠の両親も</t>
         </is>
       </c>
     </row>
-    <row r="742">
-      <c r="A742" t="inlineStr">
+    <row r="621">
+      <c r="A621" t="inlineStr">
         <is>
           <t>流石にこの時だけは
 黙っておらず
@@ -6341,16 +5478,16 @@
         </is>
       </c>
     </row>
-    <row r="743">
-      <c r="A743" t="inlineStr">
+    <row r="622">
+      <c r="A622" t="inlineStr">
         <is>
           <t>そのうち
 久遠に子供が出来たのが分かると</t>
         </is>
       </c>
     </row>
-    <row r="744">
-      <c r="A744" t="inlineStr">
+    <row r="623">
+      <c r="A623" t="inlineStr">
         <is>
           <t>手の平を返した様に
 大人しくなり、既に孫の話で
@@ -6358,8 +5495,8 @@
         </is>
       </c>
     </row>
-    <row r="745">
-      <c r="A745" t="inlineStr">
+    <row r="624">
+      <c r="A624" t="inlineStr">
         <is>
           <t>その・・・俺達の子供なんだけど
 今はまだ久遠のお腹にいて
@@ -6367,80 +5504,80 @@
         </is>
       </c>
     </row>
-    <row r="746">
-      <c r="A746" t="inlineStr">
+    <row r="625">
+      <c r="A625" t="inlineStr">
         <is>
           <t>ん・・・・・
 　　まだ・・・熱下がってないな</t>
         </is>
       </c>
     </row>
-    <row r="747">
-      <c r="A747" t="inlineStr">
+    <row r="626">
+      <c r="A626" t="inlineStr">
         <is>
           <t>ほら・・・
 　　駄目だぞ・・・ちゃんと寝てないと</t>
         </is>
       </c>
     </row>
-    <row r="748">
-      <c r="A748" t="inlineStr">
+    <row r="627">
+      <c r="A627" t="inlineStr">
         <is>
           <t>少し気怠そうな面もちで
 返事をする久遠・・・</t>
         </is>
       </c>
     </row>
-    <row r="749">
-      <c r="A749" t="inlineStr">
+    <row r="628">
+      <c r="A628" t="inlineStr">
         <is>
           <t>実は、ここ１週間ばかり
 風邪を拗らせてしまい</t>
         </is>
       </c>
     </row>
-    <row r="750">
-      <c r="A750" t="inlineStr">
+    <row r="629">
+      <c r="A629" t="inlineStr">
         <is>
           <t>予定日が近い事もあって
 病院に入院させていたのだ</t>
         </is>
       </c>
     </row>
-    <row r="751">
-      <c r="A751" t="inlineStr">
+    <row r="630">
+      <c r="A630" t="inlineStr">
         <is>
           <t>あの・・・ね
 　　お兄ちゃん・・・</t>
         </is>
       </c>
     </row>
-    <row r="752">
-      <c r="A752" t="inlineStr">
+    <row r="631">
+      <c r="A631" t="inlineStr">
         <is>
           <t>ん？
 　　今日はなんか元気無いな・・・</t>
         </is>
       </c>
     </row>
-    <row r="753">
-      <c r="A753" t="inlineStr">
+    <row r="632">
+      <c r="A632" t="inlineStr">
         <is>
           <t>もう、予定日も近いんだし
 　　元気出さないと・・・</t>
         </is>
       </c>
     </row>
-    <row r="754">
-      <c r="A754" t="inlineStr">
+    <row r="633">
+      <c r="A633" t="inlineStr">
         <is>
           <t>・・・ボクの話・・・
 　　聞いてくれないかな？</t>
         </is>
       </c>
     </row>
-    <row r="755">
-      <c r="A755" t="inlineStr">
+    <row r="634">
+      <c r="A634" t="inlineStr">
         <is>
           <t>話？
 　　なんだ・・・またなにか
@@ -6448,8 +5585,8 @@
         </is>
       </c>
     </row>
-    <row r="756">
-      <c r="A756" t="inlineStr">
+    <row r="635">
+      <c r="A635" t="inlineStr">
         <is>
           <t>そうだね・・・
 　　ボクはずっと欲しかった物があるよ
@@ -6457,15 +5594,15 @@
         </is>
       </c>
     </row>
-    <row r="757">
-      <c r="A757" t="inlineStr">
+    <row r="636">
+      <c r="A636" t="inlineStr">
         <is>
           <t>ん？なんだよ・・・それ・・・</t>
         </is>
       </c>
     </row>
-    <row r="758">
-      <c r="A758" t="inlineStr">
+    <row r="637">
+      <c r="A637" t="inlineStr">
         <is>
           <t>言っておくけど
 　　あんまり高い物は
@@ -6473,31 +5610,24 @@
         </is>
       </c>
     </row>
-    <row r="759">
-      <c r="A759" t="inlineStr">
+    <row r="638">
+      <c r="A638" t="inlineStr">
         <is>
           <t>ボクが欲しかったのは・・・
 　　たった一つの・・未来・・・</t>
         </is>
       </c>
     </row>
-    <row r="760">
-      <c r="A760" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr">
+    <row r="639">
+      <c r="A639" t="inlineStr">
         <is>
           <t>久遠がなにを
 言い出しているのか分からない</t>
         </is>
       </c>
     </row>
-    <row r="762">
-      <c r="A762" t="inlineStr">
+    <row r="640">
+      <c r="A640" t="inlineStr">
         <is>
           <t>熱のせいなのかもしれないけど
 久遠の目は至って真剣で
@@ -6505,8 +5635,8 @@
         </is>
       </c>
     </row>
-    <row r="763">
-      <c r="A763" t="inlineStr">
+    <row r="641">
+      <c r="A641" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・ごめんね・・・
 　　ずっと・・・黙ってた事
@@ -6514,8 +5644,8 @@
         </is>
       </c>
     </row>
-    <row r="764">
-      <c r="A764" t="inlineStr">
+    <row r="642">
+      <c r="A642" t="inlineStr">
         <is>
           <t>はぁ・・・
 　　また俺に内緒で
@@ -6523,24 +5653,24 @@
         </is>
       </c>
     </row>
-    <row r="765">
-      <c r="A765" t="inlineStr">
+    <row r="643">
+      <c r="A643" t="inlineStr">
         <is>
           <t>俺が久遠の頭を
 撫でながらそう言うと</t>
         </is>
       </c>
     </row>
-    <row r="766">
-      <c r="A766" t="inlineStr">
+    <row r="644">
+      <c r="A644" t="inlineStr">
         <is>
           <t>久遠はそっと目を閉じて
 俺に言う・・・</t>
         </is>
       </c>
     </row>
-    <row r="767">
-      <c r="A767" t="inlineStr">
+    <row r="645">
+      <c r="A645" t="inlineStr">
         <is>
           <t>ボクはね・・・明日・・・
 　　赤ちゃん産んで・・・そのまま
@@ -6548,8 +5678,8 @@
         </is>
       </c>
     </row>
-    <row r="768">
-      <c r="A768" t="inlineStr">
+    <row r="646">
+      <c r="A646" t="inlineStr">
         <is>
           <t>ジョーク？
 それにしてはこの時期に
@@ -6557,16 +5687,16 @@
         </is>
       </c>
     </row>
-    <row r="769">
-      <c r="A769" t="inlineStr">
+    <row r="647">
+      <c r="A647" t="inlineStr">
         <is>
           <t>俺はちょっとマジになって
 少し強く久遠に言ってしまう</t>
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
+    <row r="648">
+      <c r="A648" t="inlineStr">
         <is>
           <t>馬鹿！
 　　お前な、冗談でも言って良い事と
@@ -6574,8 +5704,8 @@
         </is>
       </c>
     </row>
-    <row r="771">
-      <c r="A771" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
         <is>
           <t>俺がそう言うと
 久遠は小さく首を横に振って
@@ -6583,47 +5713,47 @@
         </is>
       </c>
     </row>
-    <row r="772">
-      <c r="A772" t="inlineStr">
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t>最後まで・・・・
 　　黙って聞いてお兄ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="773">
-      <c r="A773" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t>ボクは・・・知ってたんだ・・・
 　　この日が来るの・・・</t>
         </is>
       </c>
     </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t>な・・・なんだよ</t>
         </is>
       </c>
     </row>
-    <row r="775">
-      <c r="A775" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t>前にも予知能力だとか・・・
 　　夢で見たとか言って</t>
         </is>
       </c>
     </row>
-    <row r="776">
-      <c r="A776" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t>何度か、お兄ちゃんの事
 　　驚かせた事・・・あったよね・・・</t>
         </is>
       </c>
     </row>
-    <row r="777">
-      <c r="A777" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t>でもね・・・それって
 　　ボクは予知してた訳じゃないんだ・・・
@@ -6631,8 +5761,8 @@
         </is>
       </c>
     </row>
-    <row r="778">
-      <c r="A778" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t>おい・・久遠・・・
 　　お前、なに馬鹿な事
@@ -6640,16 +5770,16 @@
         </is>
       </c>
     </row>
-    <row r="779">
-      <c r="A779" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t>お前が死ぬだって？？
 　　この日を知っていたって？？</t>
         </is>
       </c>
     </row>
-    <row r="780">
-      <c r="A780" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t>ボクは・・・何度も
 　　お兄ちゃんに出会って
@@ -6657,31 +5787,24 @@
         </is>
       </c>
     </row>
-    <row r="781">
-      <c r="A781" t="inlineStr">
+    <row r="659">
+      <c r="A659" t="inlineStr">
         <is>
           <t>そして別れていった・・・
 　　また、お兄ちゃんに逢う為に</t>
         </is>
       </c>
     </row>
-    <row r="782">
-      <c r="A782" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr">
+    <row r="660">
+      <c r="A660" t="inlineStr">
         <is>
           <t>だから・・・
 　　だからボクは・・・</t>
         </is>
       </c>
     </row>
-    <row r="784">
-      <c r="A784" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t>何度も、何度も
 　　自分の経験した事を利用して
@@ -6689,8 +5812,8 @@
         </is>
       </c>
     </row>
-    <row r="785">
-      <c r="A785" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t>・・・なのに
 　　・・・どうしても
@@ -6698,15 +5821,15 @@
         </is>
       </c>
     </row>
-    <row r="786">
-      <c r="A786" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t>・・・・・久遠・・・・</t>
         </is>
       </c>
     </row>
-    <row r="787">
-      <c r="A787" t="inlineStr">
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t>ごめんな・・・俺・・・久遠が
 　　なに言ってるのか・・・
@@ -6714,24 +5837,24 @@
         </is>
       </c>
     </row>
-    <row r="788">
-      <c r="A788" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t>う・・うう・・お兄ちゃん・・・
 　　ボク・・ボクはどうしたら・・・</t>
         </is>
       </c>
     </row>
-    <row r="789">
-      <c r="A789" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t>マタニティーブルーって
 ヤツなんだろうか・・・</t>
         </is>
       </c>
     </row>
-    <row r="790">
-      <c r="A790" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t>久遠はポロポロと涙を
 こぼしながら
@@ -6739,24 +5862,24 @@
         </is>
       </c>
     </row>
-    <row r="791">
-      <c r="A791" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
         <is>
           <t>俺は・・・そんな久遠を
 優しく抱き締めながら</t>
         </is>
       </c>
     </row>
-    <row r="792">
-      <c r="A792" t="inlineStr">
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t>久遠の体温を
 いつまでも感じていた・・・</t>
         </is>
       </c>
     </row>
-    <row r="793">
-      <c r="A793" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t>でもね・・・それって
 　　ボクは予知してた訳じゃないんだ・・・
@@ -6764,54 +5887,47 @@
         </is>
       </c>
     </row>
-    <row r="794">
-      <c r="A794" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t>お前が死ぬだって？？
 　　この日を知っていたって？？</t>
         </is>
       </c>
     </row>
-    <row r="795">
-      <c r="A795" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t>・・・・・久遠・・・・</t>
         </is>
       </c>
     </row>
-    <row r="797">
-      <c r="A797" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t>う・・うう・・お兄ちゃん・・・
 　　ボク・・ボクはどうしたら・・・</t>
         </is>
       </c>
     </row>
-    <row r="798">
-      <c r="A798" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t>ＥＰＩＳＯＤＥｏｆＡｌｉｖｅ
 「Ａｒｔｅｉｓｉａ」</t>
         </is>
       </c>
     </row>
-    <row r="799">
-      <c r="A799" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t>・・・・やっぱり・・・
 　　未来は変えられなかった・・・</t>
         </is>
       </c>
     </row>
-    <row r="800">
-      <c r="A800" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t>ボクが気付いた時・・・
 そこはもう・・・
@@ -6819,24 +5935,24 @@
         </is>
       </c>
     </row>
-    <row r="801">
-      <c r="A801" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t>ボクは・・・ここから
 またあの結末の未来まで・・・</t>
         </is>
       </c>
     </row>
-    <row r="802">
-      <c r="A802" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t>一体どれくらい
 繰り返してきたんだろう・・・</t>
         </is>
       </c>
     </row>
-    <row r="803">
-      <c r="A803" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t>そしてボクは走り出す
 ボクの行く場所は
@@ -6844,8 +5960,8 @@
         </is>
       </c>
     </row>
-    <row r="804">
-      <c r="A804" t="inlineStr">
+    <row r="680">
+      <c r="A680" t="inlineStr">
         <is>
           <t>ボクの中には
 お兄ちゃんとの思い出が
@@ -6853,8 +5969,8 @@
         </is>
       </c>
     </row>
-    <row r="805">
-      <c r="A805" t="inlineStr">
+    <row r="681">
+      <c r="A681" t="inlineStr">
         <is>
           <t>お兄ちゃんの良いトコも
 悪いトコもボクが誰よりも
@@ -6862,147 +5978,39 @@
         </is>
       </c>
     </row>
-    <row r="806">
-      <c r="A806" t="inlineStr">
+    <row r="682">
+      <c r="A682" t="inlineStr">
         <is>
           <t>ボクは・・・
 そんなお兄ちゃんを・・・</t>
         </is>
       </c>
     </row>
-    <row r="807">
-      <c r="A807" t="inlineStr">
+    <row r="683">
+      <c r="A683" t="inlineStr">
         <is>
           <t>ふと・・・その時・・・
 ボクの目にお兄ちゃんの姿が映る・・・</t>
         </is>
       </c>
     </row>
-    <row r="808">
-      <c r="A808" t="inlineStr">
+    <row r="684">
+      <c r="A684" t="inlineStr">
         <is>
           <t>これ、あたしの愛刀
 　　「草薙」じゃないか</t>
         </is>
       </c>
     </row>
-    <row r="809">
-      <c r="A809" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="810">
-      <c r="A810" t="inlineStr">
-        <is>
-          <t>・アルテイシア・「セリフィス・・・
-　　　私達も・・・人と同じ・・・
-　　　ただの操り人形なのかもしれないわね」</t>
-        </is>
-      </c>
-    </row>
-    <row r="811">
-      <c r="A811" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="812">
-      <c r="A812" t="inlineStr">
-        <is>
-          <t>・アルテイシア・「貴方の役目は・・・魂を導く事
-　　　　　　その魂を手元に束縛して
-　　　　　　なにを・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="813">
-      <c r="A813" t="inlineStr">
-        <is>
-          <t>・アルテイシア・「人は・・・そういうものでしょ？
-　　　　　　そして・・・私達は
-　　　　　　それを見守り、管理する」</t>
-        </is>
-      </c>
-    </row>
-    <row r="814">
-      <c r="A814" t="inlineStr">
-        <is>
-          <t>・アルテイシア・「・・・・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="815">
-      <c r="A815" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="816">
-      <c r="A816" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="818">
-      <c r="A818" t="inlineStr">
+    <row r="685">
+      <c r="A685" t="inlineStr">
         <is>
           <t>祐二！</t>
         </is>
       </c>
     </row>
-    <row r="819">
-      <c r="A819" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr">
-        <is>
-          <t>ヴァル（夜美）「・・・しつこいのね・・・
-　　　　　　セリフィス・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr">
-        <is>
-          <t>ヴァル（夜美）「久方ぶりのご挨拶・・・
-　　　それで納得出来ないのかしら？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>ヴァル（夜美）「・・・クスッ・・・
-　　　余り吠えない方がいいわよ
-　　　恥を掻くだけ・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="824">
-      <c r="A824" t="inlineStr">
+    <row r="686">
+      <c r="A686" t="inlineStr">
         <is>
           <t>・・・私は「刻の守護者」
 　　　　　人間風情ににとやかく言われる立場では
@@ -7010,8 +6018,8 @@
         </is>
       </c>
     </row>
-    <row r="825">
-      <c r="A825" t="inlineStr">
+    <row r="687">
+      <c r="A687" t="inlineStr">
         <is>
           <t>そして・・・その運命を
 　　　　　見守り、終焉に向かって
@@ -7019,8 +6027,8 @@
         </is>
       </c>
     </row>
-    <row r="826">
-      <c r="A826" t="inlineStr">
+    <row r="688">
+      <c r="A688" t="inlineStr">
         <is>
           <t>そして・・・終焉を見届け
 　　　　　新たな運命を授ける、それが
@@ -7028,53 +6036,23 @@
         </is>
       </c>
     </row>
-    <row r="827">
-      <c r="A827" t="inlineStr">
+    <row r="689">
+      <c r="A689" t="inlineStr">
         <is>
           <t>ふんふん♪</t>
         </is>
       </c>
     </row>
-    <row r="828">
-      <c r="A828" t="inlineStr">
+    <row r="690">
+      <c r="A690" t="inlineStr">
         <is>
           <t>それでは・・・
   「刻の守護者」様・・・</t>
         </is>
       </c>
     </row>
-    <row r="829">
-      <c r="A829" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr">
-        <is>
-          <t>アルテイシア「セリフィス・・・
-　　　私達も・・・人と同じ・・・
-　　　ただの操り人形なのかもしれないわね」</t>
-        </is>
-      </c>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr">
+    <row r="691">
+      <c r="A691" t="inlineStr">
         <is>
           <t>それでもアルテイシアの
 　　　「刻の守護者」の力でも
@@ -7082,8 +6060,8 @@
         </is>
       </c>
     </row>
-    <row r="834">
-      <c r="A834" t="inlineStr">
+    <row r="692">
+      <c r="A692" t="inlineStr">
         <is>
           <t>そして・・・アルテイシア様は
 　　　　　運命の狂った木原祐二に近付いた
@@ -7091,148 +6069,71 @@
         </is>
       </c>
     </row>
-    <row r="835">
-      <c r="A835" t="inlineStr">
+    <row r="693">
+      <c r="A693" t="inlineStr">
         <is>
           <t>刹那！！</t>
         </is>
       </c>
     </row>
-    <row r="836">
-      <c r="A836" t="inlineStr">
-        <is>
-          <t>アルテイシア「用・・・？
-　　　　　　心当たりが無いとでも
-　　　　　　言うのですか？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr">
-        <is>
-          <t>アルテイシア「・・・貴方の酔狂には
-　　　　　　ほとほと呆れるばかりですね・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="838">
-      <c r="A838" t="inlineStr">
-        <is>
-          <t>アルテイシア「リリス！
-　　　　　　貴方・・・自分のしている事が
-　　　　　　どういう事なのか分かってるのですか？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr">
-        <is>
-          <t>アルテイシア「・・・・・リリス・・・
-　　　　　　あくまでシラを切るのなら・・・
-　　　　　　私にも考えがあります・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="840">
-      <c r="A840" t="inlineStr">
-        <is>
-          <t>アルテイシア「貴方の役目は・・・魂を導く事
-　　　　　　その魂を手元に束縛して
-　　　　　　なにを・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="841">
-      <c r="A841" t="inlineStr">
-        <is>
-          <t>アルテイシア「人は・・・そういう物でしょ？
-　　　　　　そして・・・私達は
-　　　　　　それを見守り、管理する」</t>
-        </is>
-      </c>
-    </row>
-    <row r="842">
-      <c r="A842" t="inlineStr">
-        <is>
-          <t>アルテイシア「・・・・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="843">
-      <c r="A843" t="inlineStr">
-        <is>
-          <t>アルテイシア「リリス・・・
-　　　　　　人への干渉は・・・重大な罪
-　　　　　　それが分かっているの？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="844">
-      <c r="A844" t="inlineStr">
-        <is>
-          <t>アルテイシア「・・・・・リリス・・・
-　　　　　　人に・・なにがあると言うの・・・」</t>
-        </is>
-      </c>
-    </row>
-    <row r="845">
-      <c r="A845" t="inlineStr">
+    <row r="694">
+      <c r="A694" t="inlineStr">
         <is>
           <t>久遠・・・
 　　もう起きてていいのか？</t>
         </is>
       </c>
     </row>
-    <row r="846">
-      <c r="A846" t="inlineStr">
+    <row r="695">
+      <c r="A695" t="inlineStr">
         <is>
           <t>ん・・・・・
 　　まだ・・・熱下がってないな</t>
         </is>
       </c>
     </row>
-    <row r="847">
-      <c r="A847" t="inlineStr">
+    <row r="696">
+      <c r="A696" t="inlineStr">
         <is>
           <t>ほら・・・
 　　駄目だぞ・・・ちゃんと寝てないと</t>
         </is>
       </c>
     </row>
-    <row r="848">
-      <c r="A848" t="inlineStr">
+    <row r="697">
+      <c r="A697" t="inlineStr">
         <is>
           <t>あの・・・ね
 　　お兄ちゃん・・・</t>
         </is>
       </c>
     </row>
-    <row r="849">
-      <c r="A849" t="inlineStr">
+    <row r="698">
+      <c r="A698" t="inlineStr">
         <is>
           <t>ん？
 　　今日はなんか元気無いな・・・</t>
         </is>
       </c>
     </row>
-    <row r="850">
-      <c r="A850" t="inlineStr">
+    <row r="699">
+      <c r="A699" t="inlineStr">
         <is>
           <t>もう、予定日も近いんだし
 　　元気出さないと・・・</t>
         </is>
       </c>
     </row>
-    <row r="851">
-      <c r="A851" t="inlineStr">
+    <row r="700">
+      <c r="A700" t="inlineStr">
         <is>
           <t>・・・ボクの話・・・
 　　聞いてくれないかな？</t>
         </is>
       </c>
     </row>
-    <row r="852">
-      <c r="A852" t="inlineStr">
+    <row r="701">
+      <c r="A701" t="inlineStr">
         <is>
           <t>話？
 　　なんだ・・・またなにか
@@ -7240,8 +6141,8 @@
         </is>
       </c>
     </row>
-    <row r="853">
-      <c r="A853" t="inlineStr">
+    <row r="702">
+      <c r="A702" t="inlineStr">
         <is>
           <t>そうだね・・・
 　　ボクはずっと欲しかった物があるよ
@@ -7249,15 +6150,15 @@
         </is>
       </c>
     </row>
-    <row r="854">
-      <c r="A854" t="inlineStr">
+    <row r="703">
+      <c r="A703" t="inlineStr">
         <is>
           <t>ん？なんだよ・・・それ・・・</t>
         </is>
       </c>
     </row>
-    <row r="855">
-      <c r="A855" t="inlineStr">
+    <row r="704">
+      <c r="A704" t="inlineStr">
         <is>
           <t>言っておくけど
 　　あんまり高い物は
@@ -7265,23 +6166,16 @@
         </is>
       </c>
     </row>
-    <row r="856">
-      <c r="A856" t="inlineStr">
+    <row r="705">
+      <c r="A705" t="inlineStr">
         <is>
           <t>ボクが欲しかったのは・・・
 　　たった一つの・・未来・・・</t>
         </is>
       </c>
     </row>
-    <row r="857">
-      <c r="A857" t="inlineStr">
-        <is>
-          <t>？？？</t>
-        </is>
-      </c>
-    </row>
-    <row r="858">
-      <c r="A858" t="inlineStr">
+    <row r="706">
+      <c r="A706" t="inlineStr">
         <is>
           <t>お兄ちゃん・・・ごめんね・・・
 　　ずっと・・・黙ってた事
@@ -7289,8 +6183,8 @@
         </is>
       </c>
     </row>
-    <row r="859">
-      <c r="A859" t="inlineStr">
+    <row r="707">
+      <c r="A707" t="inlineStr">
         <is>
           <t>ボクはね・・・明日・・・
 　　赤ちゃん産んで・・・そのまま
@@ -7298,47 +6192,47 @@
         </is>
       </c>
     </row>
-    <row r="860">
-      <c r="A860" t="inlineStr">
+    <row r="708">
+      <c r="A708" t="inlineStr">
         <is>
           <t>最後まで・・・・
 　　黙って聞いてお兄ちゃん</t>
         </is>
       </c>
     </row>
-    <row r="861">
-      <c r="A861" t="inlineStr">
+    <row r="709">
+      <c r="A709" t="inlineStr">
         <is>
           <t>ボクは・・・知ってたんだ・・・
 　　この日が来るの・・・</t>
         </is>
       </c>
     </row>
-    <row r="862">
-      <c r="A862" t="inlineStr">
+    <row r="710">
+      <c r="A710" t="inlineStr">
         <is>
           <t>な・・・なんだよ</t>
         </is>
       </c>
     </row>
-    <row r="863">
-      <c r="A863" t="inlineStr">
+    <row r="711">
+      <c r="A711" t="inlineStr">
         <is>
           <t>前にも予知能力だとか・・・
 　　夢で見たとか言って</t>
         </is>
       </c>
     </row>
-    <row r="864">
-      <c r="A864" t="inlineStr">
+    <row r="712">
+      <c r="A712" t="inlineStr">
         <is>
           <t>何度か、お兄ちゃんの事
 　　驚かせた事・・・あったよね・・・</t>
         </is>
       </c>
     </row>
-    <row r="865">
-      <c r="A865" t="inlineStr">
+    <row r="713">
+      <c r="A713" t="inlineStr">
         <is>
           <t>でもね・・・それって
 　　ボクは予知してた訳じゃないんだ・・・
@@ -7346,16 +6240,16 @@
         </is>
       </c>
     </row>
-    <row r="866">
-      <c r="A866" t="inlineStr">
+    <row r="714">
+      <c r="A714" t="inlineStr">
         <is>
           <t>お前が死ぬだって？？
 　　この日を知っていたって？？</t>
         </is>
       </c>
     </row>
-    <row r="867">
-      <c r="A867" t="inlineStr">
+    <row r="715">
+      <c r="A715" t="inlineStr">
         <is>
           <t>ボクは・・・何度も
 　　お兄ちゃんに出会って
@@ -7363,23 +6257,16 @@
         </is>
       </c>
     </row>
-    <row r="868">
-      <c r="A868" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr">
+    <row r="716">
+      <c r="A716" t="inlineStr">
         <is>
           <t>だから・・・
 　　だからボクは・・・</t>
         </is>
       </c>
     </row>
-    <row r="870">
-      <c r="A870" t="inlineStr">
+    <row r="717">
+      <c r="A717" t="inlineStr">
         <is>
           <t>何度も、何度も
 　　自分の経験した事を利用して
@@ -7387,8 +6274,8 @@
         </is>
       </c>
     </row>
-    <row r="871">
-      <c r="A871" t="inlineStr">
+    <row r="718">
+      <c r="A718" t="inlineStr">
         <is>
           <t>・・・なのに
 　　・・・どうしても
@@ -7396,15 +6283,15 @@
         </is>
       </c>
     </row>
-    <row r="872">
-      <c r="A872" t="inlineStr">
+    <row r="719">
+      <c r="A719" t="inlineStr">
         <is>
           <t>・・・・・久遠・・・・</t>
         </is>
       </c>
     </row>
-    <row r="873">
-      <c r="A873" t="inlineStr">
+    <row r="720">
+      <c r="A720" t="inlineStr">
         <is>
           <t>ごめんな・・・俺・・・久遠が
 　　なに言ってるのか・・・
@@ -7412,39 +6299,16 @@
         </is>
       </c>
     </row>
-    <row r="874">
-      <c r="A874" t="inlineStr">
+    <row r="721">
+      <c r="A721" t="inlineStr">
         <is>
           <t>う・・うう・・お兄ちゃん・・・
 　　ボク・・ボクはどうしたら・・・</t>
         </is>
       </c>
     </row>
-    <row r="875">
-      <c r="A875" t="inlineStr">
-        <is>
-          <t>アルテイシア「リリス・・・
-　　　　　　人への干渉は・・・重大な罪
-　　　　　　それが分かっているの？」</t>
-        </is>
-      </c>
-    </row>
-    <row r="876">
-      <c r="A876" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr">
+    <row r="722">
+      <c r="A722" t="inlineStr">
         <is>
           <t>貴方の名前は「ヴァル」
 　　　クスクス・・・貴方には
@@ -7452,57 +6316,36 @@
         </is>
       </c>
     </row>
-    <row r="879">
-      <c r="A879" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr">
+    <row r="723">
+      <c r="A723" t="inlineStr">
         <is>
           <t>（To be continued...）</t>
         </is>
       </c>
     </row>
-    <row r="881">
-      <c r="A881" t="inlineStr">
+    <row r="724">
+      <c r="A724" t="inlineStr">
         <is>
           <t>柚！</t>
         </is>
       </c>
     </row>
-    <row r="882">
-      <c r="A882" t="inlineStr">
+    <row r="725">
+      <c r="A725" t="inlineStr">
         <is>
           <t>な・・・なんだよ</t>
         </is>
       </c>
     </row>
-    <row r="883">
-      <c r="A883" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="884">
-      <c r="A884" t="inlineStr">
-        <is>
-          <t>・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="885">
-      <c r="A885" t="inlineStr">
+    <row r="726">
+      <c r="A726" t="inlineStr">
         <is>
           <t>柚！！</t>
         </is>
       </c>
     </row>
-    <row r="886">
-      <c r="A886" t="inlineStr">
+    <row r="727">
+      <c r="A727" t="inlineStr">
         <is>
           <t>ボクはね・・・
 　　その・・・見守る・・・
@@ -7510,8 +6353,8 @@
         </is>
       </c>
     </row>
-    <row r="887">
-      <c r="A887" t="inlineStr">
+    <row r="728">
+      <c r="A728" t="inlineStr">
         <is>
           <t>ボクは・・・「刻の守護者」に戻る
 　　もう・・・途切れた運命は
@@ -7519,22 +6362,15 @@
         </is>
       </c>
     </row>
-    <row r="888">
-      <c r="A888" t="inlineStr">
+    <row r="729">
+      <c r="A729" t="inlineStr">
         <is>
           <t>？？？柚？</t>
         </is>
       </c>
     </row>
-    <row r="889">
-      <c r="A889" t="inlineStr">
-        <is>
-          <t>・・・・・・・・・・・・・・・</t>
-        </is>
-      </c>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr">
+    <row r="730">
+      <c r="A730" t="inlineStr">
         <is>
           <t>Ｅｐｉｓｏｄｅ  Ｙｕｚｕ
 ＥＮＤ</t>
